--- a/campaigns/gearbox-southern-africa/Gearbox-Leads-v3-EMAILS-PER-COMPANY.xlsx
+++ b/campaigns/gearbox-southern-africa/Gearbox-Leads-v3-EMAILS-PER-COMPANY.xlsx
@@ -378,7 +378,7 @@
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Ready to send. The person's name and their company's equipment are already written in. Replace the [BRACKETS] with your details, then paste. Your own signature goes at the end.</t>
+        <t>Ready to send as written - name, company equipment, gearbox range and lead time are all in. Copy the cell, paste, add your signature. Check the lead time matches what you can actually do.</t>
       </text>
     </comment>
   </commentList>
@@ -1175,7 +1175,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Replace every [BRACKET] with your details. No signature is included - add your own. {First} is filled in already on the Leads tab, ready to send.</t>
+          <t>Ready to send as written. Each email is addressed to the first contact at that company; the Leads tab has a copy per person. No signature - add your own.</t>
         </is>
       </c>
     </row>
@@ -1258,9 +1258,9 @@
       </c>
       <c r="H6" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Rahul,
 Plants like 260 Brands buy drive spares before the season, not during it - the mixer, conveyor and packing line drives on the plant cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -1302,9 +1302,9 @@
       </c>
       <c r="H7" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Michael,
 ACTION AUTO ZAMBIA keeps its customers running, and the drivetrain and PTO gearboxes on the vehicles you support are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -1347,9 +1347,9 @@
       </c>
       <c r="H8" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Seabi,
 At AECI Mining, the augers, mixers and conveyor drives on your emulsion plants are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -1391,9 +1391,9 @@
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Sajad,
 Access Energy Solutions Pty Ltd keeps its customers running, and the gearboxes on the plant and energy equipment you supply are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -1436,9 +1436,9 @@
       </c>
       <c r="H10" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Innocent,
 Plants like Advanta Seeds buy drive spares before the season, not during it - the seed processing, grading and conveyor drives on the plant cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -1480,9 +1480,9 @@
       </c>
       <c r="H11" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Mwila,
 At Africa Global Logistics, the materials handling, crane and conveyor drives at the terminals fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Zambia, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -1524,9 +1524,9 @@
       </c>
       <c r="H12" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Tlamelo,
 At African Mining Services, the drivetrains and final drives across your contract fleet are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -1568,9 +1568,9 @@
       </c>
       <c r="H13" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Favor,
 Applied Metrology Services (Pty) Ltd. keeps its customers running, and the gearboxes on the process equipment you calibrate and service are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Botswana.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Botswana for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -1613,9 +1613,9 @@
       </c>
       <c r="H14" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Brian,
 Plants like Austin Powder buy drive spares before the season, not during it - the mixers, augers and conveyor drives on your plant cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -1657,9 +1657,9 @@
       </c>
       <c r="H15" s="23" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Tatiana,
 Grande parte da despesa em redutores concentra-se num único fornecedor com prazos longos. Funciona até a unidade estar em rutura - e na Azule Energy isso significa os accionamentos dos guinchos, gruas e sistemas de amarração nas FPSO.
-Fornecemos redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Não é preciso mudar de fornecedor: basta consultarem-nos como segunda fonte.
 O que precisam da nossa parte para o registo de fornecedor?</t>
         </is>
@@ -1702,9 +1702,9 @@
       </c>
       <c r="H16" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Malek,
 Fábricas como a BEFCO - Indústria compram peças de transmissão antes da campanha, não durante - os accionamentos dos misturadores, transportadores e linhas de produção custam muito mais a reparar em produção do que a ter em stock.
-Fornecemos redutores [helicoidais, cónicos, planetários e de eixo oco] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos, planetários e de eixo oco - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Se me indicar a data da próxima paragem, orçamento as unidades que deveriam estar em stock antes disso.</t>
         </is>
       </c>
@@ -1746,9 +1746,9 @@
       </c>
       <c r="H17" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Dirk,
 BIA GROUP keeps its customers running, and the final drives, travel and swing drives on the machines you support are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -1791,9 +1791,9 @@
       </c>
       <c r="H18" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Cobus,
 BL&amp;D Plant Hire &amp; Sales keeps its customers running, and the gearboxes on the plant in your hire and sales fleet are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -1836,9 +1836,9 @@
       </c>
       <c r="H19" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Andries,
 At BME, a Member of the Omnia Group, the augers, mixers and pump drives on your emulsion and bulk explosives plants are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -1880,9 +1880,9 @@
       </c>
       <c r="H20" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Engmogomotsi,
 At BOTSWANA POWER CORPORATION, the coal handling conveyor, mill and ash plant drives at Morupule fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Botswana, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Botswana for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -1924,9 +1924,9 @@
       </c>
       <c r="H21" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Tshidiso,
 At Barloworld Equipment, the final drives and transmissions on the machines you support fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Botswana, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Botswana for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -1968,9 +1968,9 @@
       </c>
       <c r="H22" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Kenneth,
 At Barloworld Equipment, the final drives and transmissions on the machines you support fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Zambia, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -2012,9 +2012,9 @@
       </c>
       <c r="H23" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Sidney,
 At Barminco, the drivetrains on your underground loaders and trucks are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -2056,9 +2056,9 @@
       </c>
       <c r="H24" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Chimuka,
 At Barrick Mining Corporation, the mill and overland conveyor drives at Lumwana are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -2100,9 +2100,9 @@
       </c>
       <c r="H25" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Samson,
 Bell Equipment Mining &amp; Construction keeps its customers running, and the drivetrains and hubs on the ADTs you support are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -2145,9 +2145,9 @@
       </c>
       <c r="H26" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Bevin,
 Blumaq, S.A. keeps its customers running, and the final drives and travel drives your customers order most are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -2190,9 +2190,9 @@
       </c>
       <c r="H27" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Bofedile,
 Bofedile Tech Services (Pty) Ltd keeps its customers running, and the gearboxes on the mining and industrial equipment you supply are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Botswana.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Botswana for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -2235,9 +2235,9 @@
       </c>
       <c r="H28" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Henry,
 Bordertec Limited keeps its customers running, and the gearboxes your industrial customers ask you to source are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -2280,9 +2280,9 @@
       </c>
       <c r="H29" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Modise,
 At Botswana Ash, the dredger, conveyor and crystalliser drives at Sua Pan are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -2324,9 +2324,9 @@
       </c>
       <c r="H30" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Mpaphi,
 Plants like Botswana Meat Commission buy drive spares before the season, not during it - the conveyor, rendering and processing line drives in the abattoir cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Botswana, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Botswana for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -2368,9 +2368,9 @@
       </c>
       <c r="H31" s="23" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Ivo,
 A CENTROCAR - Centro de Equipamentos Mecânicos S.A. mantém os clientes a trabalhar, e os comandos finais, de translação e de rotação das máquinas que assistem são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -2413,9 +2413,9 @@
       </c>
       <c r="H32" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Dionisio,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na CONSUL-MARINE, isso significa os redutores dos guinchos, cabrestantes e accionamentos marítimos.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -2457,9 +2457,9 @@
       </c>
       <c r="H33" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Chanda,
 Plants like Cargill buy drive spares before the season, not during it - the mill, conveyor and elevator drives on the processing line cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -2501,9 +2501,9 @@
       </c>
       <c r="H34" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Eduardo,
 Fábricas como a Carrinho Group compram peças de transmissão antes da campanha, não durante - os accionamentos dos moinhos, transportadores e linhas de enchimento custam muito mais a reparar em produção do que a ter em stock.
-Fornecemos redutores [helicoidais, cónicos, planetários e de eixo oco] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos, planetários e de eixo oco - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Se me indicar a data da próxima paragem, orçamento as unidades que deveriam estar em stock antes disso.</t>
         </is>
       </c>
@@ -2545,9 +2545,9 @@
       </c>
       <c r="H35" s="23" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Diego,
 Fábricas como a Castel Africa compram peças de transmissão antes da campanha, não durante - os accionamentos dos transportadores, enchedoras e linhas de embalagem custam muito mais a reparar em produção do que a ter em stock.
-Fornecemos redutores [helicoidais, cónicos, planetários e de eixo oco] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos, planetários e de eixo oco - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Se me indicar a data da próxima paragem, orçamento as unidades que deveriam estar em stock antes disso.</t>
         </is>
       </c>
@@ -2589,9 +2589,9 @@
       </c>
       <c r="H36" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Stuart,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na Chevron, isso significa os accionamentos dos guinchos, gruas e equipamento rotativo offshore.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -2633,9 +2633,9 @@
       </c>
       <c r="H37" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Patson,
 Plants like Chilanga Cement Plc buy drive spares before the season, not during it - the raw mill, kiln and cement mill drives, and the clinker conveyors cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -2677,9 +2677,9 @@
       </c>
       <c r="H38" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Wessel,
 Coastal Hire keeps its customers running, and the gearboxes on the plant in your hire fleet are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Botswana.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Botswana for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -2722,9 +2722,9 @@
       </c>
       <c r="H39" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Onalenna,
 Most gearbox spend sits with a single supplier on long lead times. That works until the unit is on backorder - and at Coca-Cola Beverages Africa that means the conveyor, filler and packing line drives on the bottling hall.
-We supply [helical, bevel-helical and planetary] gearboxes and drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+We supply helical, bevel-helical and planetary gearboxes and drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 No switching required. Quote us against your current source and see where we land.
 What do you need from us for vendor registration?</t>
         </is>
@@ -2767,9 +2767,9 @@
       </c>
       <c r="H40" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Owen,
 At Copperbelt Energy Corporation Plc, the auxiliary and handling drives across the network fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Zambia, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -2811,9 +2811,9 @@
       </c>
       <c r="H41" s="23" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Claudio,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na Core Laboratories, isso significa os redutores dos equipamentos de campo e laboratório.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -2855,9 +2855,9 @@
       </c>
       <c r="H42" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Jinu,
 DGC AFRICA keeps its customers running, and the gearboxes on the industrial plant you inspect and maintain are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -2900,9 +2900,9 @@
       </c>
       <c r="H43" s="23" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Erlend,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na DOF, isso significa os redutores dos guinchos, cabrestantes e propulsores das embarcações.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -2944,9 +2944,9 @@
       </c>
       <c r="H44" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Nason,
 Plants like Dangote Industries Limited buy drive spares before the season, not during it - the raw mill, kiln and cement mill drives, and the plant conveyors cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -2988,9 +2988,9 @@
       </c>
       <c r="H45" s="23" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Badr,
 Na Dar, os redutores e accionamentos que especificam nos projectos industriais são o que pára a produção quando um redutor falha.
-A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Envie-me as unidades da vossa lista de peças críticas e respondo com preço e prazo, para terem uma segunda fonte registada antes de precisarem.</t>
         </is>
       </c>
@@ -3032,9 +3032,9 @@
       </c>
       <c r="H46" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Obakeng,
 At Debswana Diamond Company, the crusher, scrubber and DMS plant drives, and the plant conveyors at Jwaneng and Orapa are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -3076,9 +3076,9 @@
       </c>
       <c r="H47" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Tichaona,
 Delswiz Manufacturing (Pty) Limited keeps its customers running, and the gearboxes for the conveyor systems and idlers you fabricate are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Botswana.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Botswana for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -3121,9 +3121,9 @@
       </c>
       <c r="H48" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Gregory,
 Doppio Mining Equipment keeps its customers running, and the gearboxes your mining equipment customers ask for are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -3166,9 +3166,9 @@
       </c>
       <c r="H49" s="23" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Luca,
 A E.A.T.S Metering Systems mantém os clientes a trabalhar, e os redutores que acompanham os sistemas que fornecem são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -3211,9 +3211,9 @@
       </c>
       <c r="H50" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Eduardo,
 A ENCOM Lda. mantém os clientes a trabalhar, e os redutores que os vossos clientes industriais vos pedem são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -3256,9 +3256,9 @@
       </c>
       <c r="H51" s="23" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Jose,
 A ENERLINE, SA mantém os clientes a trabalhar, e os redutores dos equipamentos que instalam e mantêm são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -3301,9 +3301,9 @@
       </c>
       <c r="H52" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Vitor,
 Na ESA - Engineering Services Angola, os accionamentos dos equipamentos industriais que assistem em obra são o que pára a produção quando um redutor falha.
-A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Envie-me as unidades da vossa lista de peças críticas e respondo com preço e prazo, para terem uma segunda fonte registada antes de precisarem.</t>
         </is>
       </c>
@@ -3345,9 +3345,9 @@
       </c>
       <c r="H53" s="23" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Jose,
 A Elecnor Group mantém os clientes a trabalhar, e os accionamentos dos equipamentos de obra e das instalações que constroem são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -3390,9 +3390,9 @@
       </c>
       <c r="H54" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Ernesto,
 Grande parte da despesa em redutores concentra-se num único fornecedor com prazos longos. Funciona até a unidade estar em rutura - e na Endiama isso significa os accionamentos de britagem, lavagem e transporte nas operações mineiras.
-Fornecemos redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Não é preciso mudar de fornecedor: basta consultarem-nos como segunda fonte.
 O que precisam da nossa parte para o registo de fornecedor?</t>
         </is>
@@ -3435,9 +3435,9 @@
       </c>
       <c r="H55" s="23" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Theuns,
 Na Equipment &amp; Controls Africa, os redutores dos equipamentos industriais que assistem são o que pára a produção quando um redutor falha.
-A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Envie-me as unidades da vossa lista de peças críticas e respondo com preço e prazo, para terem uma segunda fonte registada antes de precisarem.</t>
         </is>
       </c>
@@ -3479,9 +3479,9 @@
       </c>
       <c r="H56" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Hitesh,
 Most gearbox spend sits with a single supplier on long lead times. That works until the unit is on backorder - and at Estim Construction Co. Ltd. that means the batching plant, crusher and conveyor drives on site.
-We supply [helical, bevel-helical and planetary] gearboxes and drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical and planetary gearboxes and drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 No switching required. Quote us against your current source and see where we land.
 What do you need from us for vendor registration?</t>
         </is>
@@ -3524,9 +3524,9 @@
       </c>
       <c r="H57" s="23" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Adao,
 Grande parte da despesa em redutores concentra-se num único fornecedor com prazos longos. Funciona até a unidade estar em rutura - e na ExxonMobil isso significa os accionamentos dos guinchos, gruas e equipamento rotativo offshore.
-Fornecemos redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Não é preciso mudar de fornecedor: basta consultarem-nos como segunda fonte.
 O que precisam da nossa parte para o registo de fornecedor?</t>
         </is>
@@ -3569,9 +3569,9 @@
       </c>
       <c r="H58" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Ibrahim,
 Fábricas como a FOZKUDIA Industrial Lda compram peças de transmissão antes da campanha, não durante - os accionamentos dos misturadores, transportadores e linhas de produção custam muito mais a reparar em produção do que a ter em stock.
-Fornecemos redutores [helicoidais, cónicos, planetários e de eixo oco] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos, planetários e de eixo oco - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Se me indicar a data da próxima paragem, orçamento as unidades que deveriam estar em stock antes disso.</t>
         </is>
       </c>
@@ -3613,9 +3613,9 @@
       </c>
       <c r="H59" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Anton,
 At First Quantum Minerals, the SAG and ball mill drives, overland conveyors and crusher drives at Kansanshi and Sentinel are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -3657,9 +3657,9 @@
       </c>
       <c r="H60" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Januario,
 A GEA Group mantém os clientes a trabalhar, e os redutores dos equipamentos de processo que instalam e assistem são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -3702,9 +3702,9 @@
       </c>
       <c r="H61" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Michael,
 Plants like Good Nature Agro buy drive spares before the season, not during it - the seed cleaning, grading and conveyor drives on the plant cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -3746,9 +3746,9 @@
       </c>
       <c r="H62" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Aguinaldo,
 Na Grupo Omatapalo, os accionamentos das centrais de betão, britadores e transportadores de obra são o que pára a produção quando um redutor falha.
-A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Envie-me as unidades da vossa lista de peças críticas e respondo com preço e prazo, para terem uma segunda fonte registada antes de precisarem.</t>
         </is>
       </c>
@@ -3790,9 +3790,9 @@
       </c>
       <c r="H63" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Clayton,
 HANSA-FLEX AG keeps its customers running, and the gearboxes that sit alongside the hydraulics you already supply are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Botswana.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Botswana for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -3835,9 +3835,9 @@
       </c>
       <c r="H64" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Chongo,
 Hebei Aojin Machinery Co.,Ltd. keeps its customers running, and the gearboxes on the machinery you bring into the market are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -3880,9 +3880,9 @@
       </c>
       <c r="H65" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Arne,
 Hitachi Construction Machinery keeps its customers running, and the travel and swing drives on the excavators you support are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -3925,9 +3925,9 @@
       </c>
       <c r="H66" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Busiku,
 At Ignite Energy Access, the gearboxes on the pumping and milling equipment you deploy fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Zambia, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -3969,9 +3969,9 @@
       </c>
       <c r="H67" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Zayd,
 Impex Group keeps its customers running, and the industrial and automotive gearboxes your counter customers ask for are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Botswana.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Botswana for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -4014,9 +4014,9 @@
       </c>
       <c r="H68" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Rayan,
 A Industryhub mantém os clientes a trabalhar, e os redutores que os vossos clientes industriais vos pedem são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -4059,9 +4059,9 @@
       </c>
       <c r="H69" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Tlhabologang,
 Most gearbox spend sits with a single supplier on long lead times. That works until the unit is on backorder - and at Irvine's Group that means the feed mill, conveyor and processing line drives.
-We supply [helical, bevel-helical and planetary] gearboxes and drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+We supply helical, bevel-helical and planetary gearboxes and drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 No switching required. Quote us against your current source and see where we land.
 What do you need from us for vendor registration?</t>
         </is>
@@ -4104,9 +4104,9 @@
       </c>
       <c r="H70" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Kingsley,
 At Juba Transport Limited, the drivetrain, PTO and winch gearboxes across the fleet fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Zambia, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -4148,9 +4148,9 @@
       </c>
       <c r="H71" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Sonny,
 Komatsu Africa Holdings (Pty) Ltd keeps its customers running, and your customers' excavator final drives, travel and swing drives are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Botswana.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Botswana for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -4193,9 +4193,9 @@
       </c>
       <c r="H72" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Vinod,
 At Konkola Copper Mines plc, the concentrator mill drives, shaft winders and tailings leach plant drives at Konkola and Nchanga are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -4237,9 +4237,9 @@
       </c>
       <c r="H73" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Mothobi,
 Plants like Lactalis Group buy drive spares before the season, not during it - the homogeniser, conveyor and packing line drives on the dairy cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Botswana, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Botswana for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -4281,9 +4281,9 @@
       </c>
       <c r="H74" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Yogen,
 At Lake Oil Group, the pump, drivetrain and handling drives across the fleet and depots fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Zambia, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -4325,9 +4325,9 @@
       </c>
       <c r="H75" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Henri,
 Liebherr Group keeps its customers running, and the final and travel drives on the mining machines you support are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -4370,9 +4370,9 @@
       </c>
       <c r="H76" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Noboth,
 At Lucient Engineering and Construction (Pty) Ltd, the gearboxes on the plant and equipment you run on site fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Botswana, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Botswana for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -4414,9 +4414,9 @@
       </c>
       <c r="H77" s="23" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Josemar,
 Fábricas como a MAXAM compram peças de transmissão antes da campanha, não durante - os accionamentos dos misturadores, sem-fins e transportadores da fábrica custam muito mais a reparar em produção do que a ter em stock.
-Fornecemos redutores [helicoidais, cónicos, planetários e de eixo oco] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos, planetários e de eixo oco - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Se me indicar a data da próxima paragem, orçamento as unidades que deveriam estar em stock antes disso.</t>
         </is>
       </c>
@@ -4458,9 +4458,9 @@
       </c>
       <c r="H78" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Pradeep,
 Na Marlin Natural Stones, os accionamentos das serras, britadores e transportadores da pedreira são o que pára a produção quando um redutor falha.
-A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Envie-me as unidades da vossa lista de peças críticas e respondo com preço e prazo, para terem uma segunda fonte registada antes de precisarem.</t>
         </is>
       </c>
@@ -4502,9 +4502,9 @@
       </c>
       <c r="H79" s="23" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Nasim,
 A Mega Mecanix mantém os clientes a trabalhar, e os redutores dos equipamentos industriais que fornecem são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -4547,9 +4547,9 @@
       </c>
       <c r="H80" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Aurelio,
 Na Metalosul, os accionamentos das máquinas de transformação e das linhas de produção são o que pára a produção quando um redutor falha.
-A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Envie-me as unidades da vossa lista de peças críticas e respondo com preço e prazo, para terem uma segunda fonte registada antes de precisarem.</t>
         </is>
       </c>
@@ -4591,9 +4591,9 @@
       </c>
       <c r="H81" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Edwin,
 At Minergy Ltd, the crushing and screening plant drives at Masama are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -4635,9 +4635,9 @@
       </c>
       <c r="H82" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Tozyani,
 At Mopani Copper Mines Plc, the shaft hoists, concentrator mills and smelter conveyor drives at Mufulira and Nkana are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -4679,9 +4679,9 @@
       </c>
       <c r="H83" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Mothusi,
 At Morupule Coal Mine, the coal conveyor, crusher and screen drives on the plant are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -4723,9 +4723,9 @@
       </c>
       <c r="H84" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Ranjeet,
 Plants like Mount Meru Group buy drive spares before the season, not during it - the expeller, conveyor and refinery drives on the oil plant cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -4767,9 +4767,9 @@
       </c>
       <c r="H85" s="23" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Paulo,
 A Movicortes Angola mantém os clientes a trabalhar, e os redutores das máquinas e equipamentos que comercializam são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -4812,9 +4812,9 @@
       </c>
       <c r="H86" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Peter,
 A Nampak mantém os clientes a trabalhar, e os accionamentos das prensas, transportadores e linhas de embalagem são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -4857,9 +4857,9 @@
       </c>
       <c r="H87" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Gabriel,
 Most gearbox spend sits with a single supplier on long lead times. That works until the unit is on backorder - and at National Milling Corporation Limited that means the roller mill, conveyor and bucket elevator drives on the mill.
-We supply [helical, bevel-helical and planetary] gearboxes and drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical and planetary gearboxes and drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 No switching required. Quote us against your current source and see where we land.
 What do you need from us for vendor registration?</t>
         </is>
@@ -4902,9 +4902,9 @@
       </c>
       <c r="H88" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Kitana,
 A Nors Group mantém os clientes a trabalhar, e os comandos finais e caixas das máquinas e camiões que assistem no pós-venda são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -4947,9 +4947,9 @@
       </c>
       <c r="H89" s="23" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Mario,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na OCEANBIZZ, isso significa os redutores dos guinchos e accionamentos marítimos.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -4991,9 +4991,9 @@
       </c>
       <c r="H90" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Jean,
 A OG3S Mecanica Lda mantém os clientes a trabalhar, e os redutores dos equipamentos industriais que assistem são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -5036,9 +5036,9 @@
       </c>
       <c r="H91" s="23" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá William,
 Na Odebrecht Engenharia &amp; Construção, os accionamentos das centrais de betão, gruas e equipamento de obra são o que pára a produção quando um redutor falha.
-A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Envie-me as unidades da vossa lista de peças críticas e respondo com preço e prazo, para terem uma segunda fonte registada antes de precisarem.</t>
         </is>
       </c>
@@ -5080,9 +5080,9 @@
       </c>
       <c r="H92" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Milton,
 Plants like Olam buy drive spares before the season, not during it - the mill, conveyor and elevator drives on the processing line cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -5124,9 +5124,9 @@
       </c>
       <c r="H93" s="23" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Giuseppe,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na PETROBEL, isso significa os accionamentos dos guinchos e equipamento rotativo em terra.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -5168,9 +5168,9 @@
       </c>
       <c r="H94" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Antonio,
 Na PROMETIM, os redutores que passam pela vossa oficina de manutenção industrial são o que pára a produção quando um redutor falha.
-A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Envie-me as unidades da vossa lista de peças críticas e respondo com preço e prazo, para terem uma segunda fonte registada antes de precisarem.</t>
         </is>
       </c>
@@ -5212,9 +5212,9 @@
       </c>
       <c r="H95" s="23" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Kelson,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na PWSIX LDA, isso significa os redutores dos equipamentos que operam em campo.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -5256,9 +5256,9 @@
       </c>
       <c r="H96" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Donald,
 At Pacific Logistics, the drivetrain and materials handling drives across the fleet fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Botswana, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Botswana for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -5300,9 +5300,9 @@
       </c>
       <c r="H97" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Kago,
 Most gearbox spend sits with a single supplier on long lead times. That works until the unit is on backorder - and at PepsiCo that means the conveyor, filler and packing line drives on the bottling hall.
-We supply [helical, bevel-helical and planetary] gearboxes and drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+We supply helical, bevel-helical and planetary gearboxes and drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 No switching required. Quote us against your current source and see where we land.
 What do you need from us for vendor registration?</t>
         </is>
@@ -5345,9 +5345,9 @@
       </c>
       <c r="H98" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Igor,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na Perbras, isso significa os redutores dos guinchos e equipamento rotativo de campo.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -5389,9 +5389,9 @@
       </c>
       <c r="H99" s="23" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Francisco,
 Grande parte da despesa em redutores concentra-se num único fornecedor com prazos longos. Funciona até a unidade estar em rutura - e na Petromar Lda isso significa os accionamentos dos guinchos, gruas e equipamento de fabricação.
-Fornecemos redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Não é preciso mudar de fornecedor: basta consultarem-nos como segunda fonte.
 O que precisam da nossa parte para o registo de fornecedor?</t>
         </is>
@@ -5434,9 +5434,9 @@
       </c>
       <c r="H100" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Nembamba,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na Puma Energy, isso significa os accionamentos das bombas e equipamento de movimentação nos terminais.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -5478,9 +5478,9 @@
       </c>
       <c r="H101" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Molebedi,
 At Puma Energy Botswana Pty. Ltd., the pump and handling drives at the terminals and depots fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Botswana, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Botswana for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -5522,9 +5522,9 @@
       </c>
       <c r="H102" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Lidia,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na Pumangol, isso significa os accionamentos das bombas e equipamento de movimentação nos terminais.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -5566,9 +5566,9 @@
       </c>
       <c r="H103" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Yoginder,
 R A Consulting Services (RACS) keeps its customers running, and the gearboxes on the plant that passes through your workshop are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -5611,9 +5611,9 @@
       </c>
       <c r="H104" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Gildo,
 Grande parte da despesa em redutores concentra-se num único fornecedor com prazos longos. Funciona até a unidade estar em rutura - e na Refriango isso significa os accionamentos dos transportadores, enchedoras e linhas de embalagem.
-Fornecemos redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Não é preciso mudar de fornecedor: basta consultarem-nos como segunda fonte.
 O que precisam da nossa parte para o registo de fornecedor?</t>
         </is>
@@ -5656,9 +5656,9 @@
       </c>
       <c r="H105" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Donovan,
 Rotating Solutions Botswana keeps its customers running, and the gearboxes that sit alongside the bearings and pumps you already distribute are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Botswana.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Botswana for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -5701,9 +5701,9 @@
       </c>
       <c r="H106" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Robert,
 Plants like Royal De Heus buy drive spares before the season, not during it - the hammer mill, pellet mill and conveyor drives on the feed mill cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -5745,9 +5745,9 @@
       </c>
       <c r="H107" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Michael,
 At SABOT Group, the drivetrain, PTO and winch gearboxes across the fleet fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Zambia, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -5789,9 +5789,9 @@
       </c>
       <c r="H108" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Simon,
 SAFE KAHYA Limited keeps its customers running, and the gearboxes your industrial customers ask you to source are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -5834,9 +5834,9 @@
       </c>
       <c r="H109" s="23" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Carlos,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na SONILS - Sonangol Integrated Logistics Services, isso significa os accionamentos das gruas, pórtico e equipamento de movimentação da base.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -5878,9 +5878,9 @@
       </c>
       <c r="H110" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Luis,
 A SPIE Global Services Energy mantém os clientes a trabalhar, e os redutores dos equipamentos rotativos que mantêm em operação são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -5923,9 +5923,9 @@
       </c>
       <c r="H111" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Tshegofatso,
 Most gearbox spend sits with a single supplier on long lead times. That works until the unit is on backorder - and at SPTC that means the gearboxes that pair with the electrical equipment you supply.
-We supply [helical, bevel-helical and planetary] gearboxes and drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+We supply helical, bevel-helical and planetary gearboxes and drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 No switching required. Quote us against your current source and see where we land.
 What do you need from us for vendor registration?</t>
         </is>
@@ -5968,9 +5968,9 @@
       </c>
       <c r="H112" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Otlhokilwe,
 Plants like Saint-Gobain buy drive spares before the season, not during it - the mixer, conveyor and press drives on the plant cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Botswana, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Botswana for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -6012,9 +6012,9 @@
       </c>
       <c r="H113" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Onnete,
 At Sandfire, the mill and conveyor drives on the Motheo circuit are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -6056,9 +6056,9 @@
       </c>
       <c r="H114" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Ashok,
 Saro Agro Industrial Ltd keeps its customers running, and the gearboxes on the implements, irrigation and processing equipment you sell are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -6101,9 +6101,9 @@
       </c>
       <c r="H115" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Tim,
 Scamont and Karlsons Mining Solutions (SKMS) keeps its customers running, and the gearboxes on the mining equipment you supply and support are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -6146,9 +6146,9 @@
       </c>
       <c r="H116" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Justin,
 Selected Supplies keeps its customers running, and the gearboxes your industrial and mining customers ask for are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -6191,9 +6191,9 @@
       </c>
       <c r="H117" s="23" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Marcelino,
 Fábricas como a Siemens compram peças de transmissão antes da campanha, não durante - os redutores dos accionamentos e equipamentos que instalam e assistem custam muito mais a reparar em produção do que a ter em stock.
-Fornecemos redutores [helicoidais, cónicos, planetários e de eixo oco] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos, planetários e de eixo oco - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Se me indicar a data da próxima paragem, orçamento as unidades que deveriam estar em stock antes disso.</t>
         </is>
       </c>
@@ -6235,9 +6235,9 @@
       </c>
       <c r="H118" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Tomas,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na Siemens Energy, isso significa os redutores das turbinas, geradores e accionamentos auxiliares.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -6279,9 +6279,9 @@
       </c>
       <c r="H119" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Patrick,
 At Simba Group, the drivetrain and materials handling drives across the fleet fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Zambia, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -6323,9 +6323,9 @@
       </c>
       <c r="H120" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Dario,
 Na Sociedade Mineira de Catoca, os accionamentos dos britadores, lavadores e transportadores da lavaria são o que pára a produção quando um redutor falha.
-A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Envie-me as unidades da vossa lista de peças críticas e respondo com preço e prazo, para terem uma segunda fonte registada antes de precisarem.</t>
         </is>
       </c>
@@ -6367,9 +6367,9 @@
       </c>
       <c r="H121" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Robert,
 Sulzer keeps its customers running, and the gearboxes driving the pumps and rotating equipment you service are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -6412,9 +6412,9 @@
       </c>
       <c r="H122" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Mwendo,
 Plants like Synergy Seeds Zambia buy drive spares before the season, not during it - the seed cleaner, grader and conveyor drives on the plant cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -6456,9 +6456,9 @@
       </c>
       <c r="H123" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi James,
 Plants like TATA Zambia buy drive spares before the season, not during it - the gearboxes on the plant and vehicles you run cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -6500,9 +6500,9 @@
       </c>
       <c r="H124" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Nicolas,
 A TFE GROUP INC mantém os clientes a trabalhar, e os redutores que os vossos clientes industriais vos pedem são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -6545,9 +6545,9 @@
       </c>
       <c r="H125" s="23" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá James,
 Na TechnipFMC, os accionamentos dos guinchos, gruas e equipamento de fabricação são o que pára a produção quando um redutor falha.
-A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Envie-me as unidades da vossa lista de peças críticas e respondo com preço e prazo, para terem uma segunda fonte registada antes de precisarem.</t>
         </is>
       </c>
@@ -6589,9 +6589,9 @@
       </c>
       <c r="H126" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Carlos,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na TotalEnergies, isso significa os accionamentos dos guinchos, gruas e equipamento rotativo offshore.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -6633,9 +6633,9 @@
       </c>
       <c r="H127" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Jones,
 Plants like Trade Kings Group buy drive spares before the season, not during it - the mixer, conveyor and packing line drives across the plant cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -6677,9 +6677,9 @@
       </c>
       <c r="H128" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Airborne,
 At UMS Group (United Mining Services), the winders, hoists and shaft equipment you install and maintain are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -6721,9 +6721,9 @@
       </c>
       <c r="H129" s="23" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Bruno,
 Fábricas como a Unique Beverages SA compram peças de transmissão antes da campanha, não durante - os accionamentos dos transportadores e da linha de enchimento custam muito mais a reparar em produção do que a ter em stock.
-Fornecemos redutores [helicoidais, cónicos, planetários e de eixo oco] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos, planetários e de eixo oco - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Se me indicar a data da próxima paragem, orçamento as unidades que deveriam estar em stock antes disso.</t>
         </is>
       </c>
@@ -6765,9 +6765,9 @@
       </c>
       <c r="H130" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Madalitso,
 Unirate Investments Limited keeps its customers running, and the gearboxes your industrial customers ask you to source are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -6810,9 +6810,9 @@
       </c>
       <c r="H131" s="23" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Domingos,
 Fábricas como a Unotech, LDA compram peças de transmissão antes da campanha, não durante - os redutores dos equipamentos industriais que assistem custam muito mais a reparar em produção do que a ter em stock.
-Fornecemos redutores [helicoidais, cónicos, planetários e de eixo oco] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos, planetários e de eixo oco - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Se me indicar a data da próxima paragem, orçamento as unidades que deveriam estar em stock antes disso.</t>
         </is>
       </c>
@@ -6854,9 +6854,9 @@
       </c>
       <c r="H132" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Chanda,
 Most gearbox spend sits with a single supplier on long lead times. That works until the unit is on backorder - and at VARUN BEVERAGES LIMITED that means the conveyor, filler and packing line drives on the bottling hall.
-We supply [helical, bevel-helical and planetary] gearboxes and drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical and planetary gearboxes and drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 No switching required. Quote us against your current source and see where we land.
 What do you need from us for vendor registration?</t>
         </is>
@@ -6899,9 +6899,9 @@
       </c>
       <c r="H133" s="23" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Emil,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na Victory Oil &amp; Energy, isso significa os redutores dos guinchos e equipamento de intervenção em poço.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -6943,9 +6943,9 @@
       </c>
       <c r="H134" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Idah,
 Most gearbox spend sits with a single supplier on long lead times. That works until the unit is on backorder - and at Vivo Energy that means the pump, loading arm and handling drives at the terminals.
-We supply [helical, bevel-helical and planetary] gearboxes and drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+We supply helical, bevel-helical and planetary gearboxes and drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 No switching required. Quote us against your current source and see where we land.
 What do you need from us for vendor registration?</t>
         </is>
@@ -6988,9 +6988,9 @@
       </c>
       <c r="H135" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Gregory,
 At Vivo Energy, the pump, loading arm and handling drives at the terminals fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Zambia, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -7032,9 +7032,9 @@
       </c>
       <c r="H136" s="19" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Jose,
 Grande parte da despesa em redutores concentra-se num único fornecedor com prazos longos. Funciona até a unidade estar em rutura - e na Webcor Group isso significa os accionamentos dos moinhos de rolos, transportadores e elevadores de alcatruzes.
-Fornecemos redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Não é preciso mudar de fornecedor: basta consultarem-nos como segunda fonte.
 O que precisam da nossa parte para o registo de fornecedor?</t>
         </is>
@@ -7077,9 +7077,9 @@
       </c>
       <c r="H137" s="23" t="inlineStr">
         <is>
-          <t>Olá {First},
+          <t>Olá Mathieu,
 A Welltec mantém os clientes a trabalhar, e os redutores e accionamentos dos guinchos e equipamentos de intervenção são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -7122,9 +7122,9 @@
       </c>
       <c r="H138" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Mlayana,
 Younique Engineering Limited keeps its customers running, and the gearboxes your industrial clients ask you to source are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -7167,9 +7167,9 @@
       </c>
       <c r="H139" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Roger,
 Plants like Yoyo Foods buy drive spares before the season, not during it - the mixer, conveyor and packing line drives on the plant cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -7211,9 +7211,9 @@
       </c>
       <c r="H140" s="19" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Agripa,
 At ZESCO, the gate, crane and auxiliary drives on the hydro stations fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Zambia, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -7255,9 +7255,9 @@
       </c>
       <c r="H141" s="23" t="inlineStr">
         <is>
-          <t>Hi {First},
+          <t>Hi Justice,
 ZISMO Engineering (Pty) Ltd. keeps its customers running, and the gearboxes that pair with the motors and drives you already rebuild are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Botswana.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Botswana for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -7480,7 +7480,7 @@
         <is>
           <t>Olá Ivo,
 A CENTROCAR - Centro de Equipamentos Mecânicos S.A. mantém os clientes a trabalhar, e os comandos finais, de translação e de rotação das máquinas que assistem são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -7588,7 +7588,7 @@
         <is>
           <t>Olá Luca,
 A E.A.T.S Metering Systems mantém os clientes a trabalhar, e os redutores que acompanham os sistemas que fornecem são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -7696,7 +7696,7 @@
         <is>
           <t>Olá Eduardo,
 A ENCOM Lda. mantém os clientes a trabalhar, e os redutores que os vossos clientes industriais vos pedem são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -7804,7 +7804,7 @@
         <is>
           <t>Olá Jose,
 A ENERLINE, SA mantém os clientes a trabalhar, e os redutores dos equipamentos que instalam e mantêm são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -7908,7 +7908,7 @@
         <is>
           <t>Olá Jose,
 A Elecnor Group mantém os clientes a trabalhar, e os accionamentos dos equipamentos de obra e das instalações que constroem são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -8012,7 +8012,7 @@
         <is>
           <t>Olá Januario,
 A GEA Group mantém os clientes a trabalhar, e os redutores dos equipamentos de processo que instalam e assistem são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -8124,7 +8124,7 @@
         <is>
           <t>Olá Rayan,
 A Industryhub mantém os clientes a trabalhar, e os redutores que os vossos clientes industriais vos pedem são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -8224,7 +8224,7 @@
         <is>
           <t>Olá Nasim,
 A Mega Mecanix mantém os clientes a trabalhar, e os redutores dos equipamentos industriais que fornecem são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -8332,7 +8332,7 @@
         <is>
           <t>Olá Paulo,
 A Movicortes Angola mantém os clientes a trabalhar, e os redutores das máquinas e equipamentos que comercializam são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -8436,7 +8436,7 @@
         <is>
           <t>Olá Peter,
 A Nampak mantém os clientes a trabalhar, e os accionamentos das prensas, transportadores e linhas de embalagem são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -8548,7 +8548,7 @@
         <is>
           <t>Olá Kitana,
 A Nors Group mantém os clientes a trabalhar, e os comandos finais e caixas das máquinas e camiões que assistem no pós-venda são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -8656,7 +8656,7 @@
         <is>
           <t>Olá Jean,
 A OG3S Mecanica Lda mantém os clientes a trabalhar, e os redutores dos equipamentos industriais que assistem são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -8760,7 +8760,7 @@
         <is>
           <t>Olá Luis,
 A SPIE Global Services Energy mantém os clientes a trabalhar, e os redutores dos equipamentos rotativos que mantêm em operação são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -8868,7 +8868,7 @@
         <is>
           <t>Olá Nicolas,
 A TFE GROUP INC mantém os clientes a trabalhar, e os redutores que os vossos clientes industriais vos pedem são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -8976,7 +8976,7 @@
         <is>
           <t>Olá Mathieu,
 A Welltec mantém os clientes a trabalhar, e os redutores e accionamentos dos guinchos e equipamentos de intervenção são o que fica parado quando um redutor está em falta.
-Fornecemos redutores industriais e móveis - [helicoidais, cónicos, planetários, comandos de translação e rotação] - a preços de revenda, [X] dias até Angola.
+Fornecemos redutores industriais e móveis - helicoidais, cónicos, planetários, comandos de translação e rotação - a preços de revenda, 10 a 14 dias até Angola para as medidas em stock.
 A maioria dos distribuidores com quem trabalhamos mantém um pequeno stock das unidades que mais substituem, para resolver uma avaria na mesma semana em vez de esperar seis.
 Posso enviar a nossa gama e preços de revenda?</t>
         </is>
@@ -9084,7 +9084,7 @@
         <is>
           <t>Hi Favor,
 Applied Metrology Services (Pty) Ltd. keeps its customers running, and the gearboxes on the process equipment you calibrate and service are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Botswana.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Botswana for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -9196,7 +9196,7 @@
         <is>
           <t>Hi Bofedile,
 Bofedile Tech Services (Pty) Ltd keeps its customers running, and the gearboxes on the mining and industrial equipment you supply are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Botswana.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Botswana for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -9296,7 +9296,7 @@
         <is>
           <t>Hi Wessel,
 Coastal Hire keeps its customers running, and the gearboxes on the plant in your hire fleet are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Botswana.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Botswana for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -9408,7 +9408,7 @@
         <is>
           <t>Hi Tichaona,
 Delswiz Manufacturing (Pty) Limited keeps its customers running, and the gearboxes for the conveyor systems and idlers you fabricate are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Botswana.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Botswana for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -9512,7 +9512,7 @@
         <is>
           <t>Hi Clayton,
 HANSA-FLEX AG keeps its customers running, and the gearboxes that sit alongside the hydraulics you already supply are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Botswana.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Botswana for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -9620,7 +9620,7 @@
         <is>
           <t>Hi Zayd,
 Impex Group keeps its customers running, and the industrial and automotive gearboxes your counter customers ask for are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Botswana.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Botswana for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -9720,7 +9720,7 @@
         <is>
           <t>Hi Sonny,
 Komatsu Africa Holdings (Pty) Ltd keeps its customers running, and your customers' excavator final drives, travel and swing drives are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Botswana.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Botswana for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -9828,7 +9828,7 @@
         <is>
           <t>Hi Donovan,
 Rotating Solutions Botswana keeps its customers running, and the gearboxes that sit alongside the bearings and pumps you already distribute are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Botswana.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Botswana for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -9928,7 +9928,7 @@
         <is>
           <t>Hi Tshegofatso,
 Most gearbox spend sits with a single supplier on long lead times. That works until the unit is on backorder - and at SPTC that means the gearboxes that pair with the electrical equipment you supply.
-We supply [helical, bevel-helical and planetary] gearboxes and drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+We supply helical, bevel-helical and planetary gearboxes and drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 No switching required. Quote us against your current source and see where we land.
 What do you need from us for vendor registration?</t>
         </is>
@@ -10040,7 +10040,7 @@
         <is>
           <t>Hi Justice,
 ZISMO Engineering (Pty) Ltd. keeps its customers running, and the gearboxes that pair with the motors and drives you already rebuild are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Botswana.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Botswana for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -10144,7 +10144,7 @@
         <is>
           <t>Hi Michael,
 ACTION AUTO ZAMBIA keeps its customers running, and the drivetrain and PTO gearboxes on the vehicles you support are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -10244,7 +10244,7 @@
         <is>
           <t>Hi Sajad,
 Access Energy Solutions Pty Ltd keeps its customers running, and the gearboxes on the plant and energy equipment you supply are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -10348,7 +10348,7 @@
         <is>
           <t>Hi Dirk,
 BIA GROUP keeps its customers running, and the final drives, travel and swing drives on the machines you support are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -10456,7 +10456,7 @@
         <is>
           <t>Hi Cobus,
 BL&amp;D Plant Hire &amp; Sales keeps its customers running, and the gearboxes on the plant in your hire and sales fleet are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -10556,7 +10556,7 @@
         <is>
           <t>Hi Samson,
 Bell Equipment Mining &amp; Construction keeps its customers running, and the drivetrains and hubs on the ADTs you support are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -10668,7 +10668,7 @@
         <is>
           <t>Hi Bevin,
 Blumaq, S.A. keeps its customers running, and the final drives and travel drives your customers order most are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -10776,7 +10776,7 @@
         <is>
           <t>Hi Henry,
 Bordertec Limited keeps its customers running, and the gearboxes your industrial customers ask you to source are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -10876,7 +10876,7 @@
         <is>
           <t>Hi Jinu,
 DGC AFRICA keeps its customers running, and the gearboxes on the industrial plant you inspect and maintain are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -10984,7 +10984,7 @@
         <is>
           <t>Hi Gregory,
 Doppio Mining Equipment keeps its customers running, and the gearboxes your mining equipment customers ask for are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -11084,7 +11084,7 @@
         <is>
           <t>Hi Chongo,
 Hebei Aojin Machinery Co.,Ltd. keeps its customers running, and the gearboxes on the machinery you bring into the market are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -11192,7 +11192,7 @@
         <is>
           <t>Hi Arne,
 Hitachi Construction Machinery keeps its customers running, and the travel and swing drives on the excavators you support are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -11300,7 +11300,7 @@
         <is>
           <t>Hi Henri,
 Liebherr Group keeps its customers running, and the final and travel drives on the mining machines you support are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -11408,7 +11408,7 @@
         <is>
           <t>Hi Yoginder,
 R A Consulting Services (RACS) keeps its customers running, and the gearboxes on the plant that passes through your workshop are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -11512,7 +11512,7 @@
         <is>
           <t>Hi Simon,
 SAFE KAHYA Limited keeps its customers running, and the gearboxes your industrial customers ask you to source are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -11612,7 +11612,7 @@
         <is>
           <t>Hi Ashok,
 Saro Agro Industrial Ltd keeps its customers running, and the gearboxes on the implements, irrigation and processing equipment you sell are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -11716,7 +11716,7 @@
         <is>
           <t>Hi Tim,
 Scamont and Karlsons Mining Solutions (SKMS) keeps its customers running, and the gearboxes on the mining equipment you supply and support are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -11816,7 +11816,7 @@
         <is>
           <t>Hi Justin,
 Selected Supplies keeps its customers running, and the gearboxes your industrial and mining customers ask for are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -11924,7 +11924,7 @@
         <is>
           <t>Hi Sean,
 Selected Supplies keeps its customers running, and the gearboxes your industrial and mining customers ask for are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -12036,7 +12036,7 @@
         <is>
           <t>Hi Robert,
 Sulzer keeps its customers running, and the gearboxes driving the pumps and rotating equipment you service are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -12144,7 +12144,7 @@
         <is>
           <t>Hi Madalitso,
 Unirate Investments Limited keeps its customers running, and the gearboxes your industrial customers ask you to source are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -12248,7 +12248,7 @@
         <is>
           <t>Hi Mlayana,
 Younique Engineering Limited keeps its customers running, and the gearboxes your industrial clients ask you to source are what sit idle when a gearbox is on backorder.
-We supply industrial and mobile gearboxes - [helical, bevel-helical, planetary, travel and swing drives] - at trade pricing, [X] days into Zambia.
+We supply industrial and mobile gearboxes - helical, bevel-helical, planetary, travel and swing drives - at trade pricing, 10 to 14 days into Zambia for stocked sizes.
 Most distributors we work with hold a small consignment of the units they move most, so a breakdown becomes a same-week fix instead of a six-week import.
 Can I send our range and dealer pricing?</t>
         </is>
@@ -12352,7 +12352,7 @@
         <is>
           <t>Olá Badr,
 Na Dar, os redutores e accionamentos que especificam nos projectos industriais são o que pára a produção quando um redutor falha.
-A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Envie-me as unidades da vossa lista de peças críticas e respondo com preço e prazo, para terem uma segunda fonte registada antes de precisarem.</t>
         </is>
       </c>
@@ -12463,7 +12463,7 @@
         <is>
           <t>Olá Georges,
 Na Dar, os redutores e accionamentos que especificam nos projectos industriais são o que pára a produção quando um redutor falha.
-A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Envie-me as unidades da vossa lista de peças críticas e respondo com preço e prazo, para terem uma segunda fonte registada antes de precisarem.</t>
         </is>
       </c>
@@ -12570,7 +12570,7 @@
         <is>
           <t>Olá Vitor,
 Na ESA - Engineering Services Angola, os accionamentos dos equipamentos industriais que assistem em obra são o que pára a produção quando um redutor falha.
-A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Envie-me as unidades da vossa lista de peças críticas e respondo com preço e prazo, para terem uma segunda fonte registada antes de precisarem.</t>
         </is>
       </c>
@@ -12665,7 +12665,7 @@
         <is>
           <t>Olá Rosmely,
 Na Elecnor Group, os accionamentos dos equipamentos de obra e das instalações que constroem são o que pára a produção quando um redutor falha.
-A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Envie-me as unidades da vossa lista de peças críticas e respondo com preço e prazo, para terem uma segunda fonte registada antes de precisarem.</t>
         </is>
       </c>
@@ -12772,7 +12772,7 @@
         <is>
           <t>Olá Ernesto,
 Grande parte da despesa em redutores concentra-se num único fornecedor com prazos longos. Funciona até a unidade estar em rutura - e na Endiama isso significa os accionamentos de britagem, lavagem e transporte nas operações mineiras.
-Fornecemos redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Não é preciso mudar de fornecedor: basta consultarem-nos como segunda fonte.
 O que precisam da nossa parte para o registo de fornecedor?</t>
         </is>
@@ -12880,7 +12880,7 @@
         <is>
           <t>Olá Theuns,
 Na Equipment &amp; Controls Africa, os redutores dos equipamentos industriais que assistem são o que pára a produção quando um redutor falha.
-A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Envie-me as unidades da vossa lista de peças críticas e respondo com preço e prazo, para terem uma segunda fonte registada antes de precisarem.</t>
         </is>
       </c>
@@ -12991,7 +12991,7 @@
         <is>
           <t>Olá Aguinaldo,
 Na Grupo Omatapalo, os accionamentos das centrais de betão, britadores e transportadores de obra são o que pára a produção quando um redutor falha.
-A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Envie-me as unidades da vossa lista de peças críticas e respondo com preço e prazo, para terem uma segunda fonte registada antes de precisarem.</t>
         </is>
       </c>
@@ -13098,7 +13098,7 @@
         <is>
           <t>Olá Pradeep,
 Na Marlin Natural Stones, os accionamentos das serras, britadores e transportadores da pedreira são o que pára a produção quando um redutor falha.
-A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Envie-me as unidades da vossa lista de peças críticas e respondo com preço e prazo, para terem uma segunda fonte registada antes de precisarem.</t>
         </is>
       </c>
@@ -13201,7 +13201,7 @@
         <is>
           <t>Olá Aurelio,
 Na Metalosul, os accionamentos das máquinas de transformação e das linhas de produção são o que pára a produção quando um redutor falha.
-A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Envie-me as unidades da vossa lista de peças críticas e respondo com preço e prazo, para terem uma segunda fonte registada antes de precisarem.</t>
         </is>
       </c>
@@ -13308,7 +13308,7 @@
         <is>
           <t>Olá William,
 Na Odebrecht Engenharia &amp; Construção, os accionamentos das centrais de betão, gruas e equipamento de obra são o que pára a produção quando um redutor falha.
-A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Envie-me as unidades da vossa lista de peças críticas e respondo com preço e prazo, para terem uma segunda fonte registada antes de precisarem.</t>
         </is>
       </c>
@@ -13411,7 +13411,7 @@
         <is>
           <t>Olá Antonio,
 Na PROMETIM, os redutores que passam pela vossa oficina de manutenção industrial são o que pára a produção quando um redutor falha.
-A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Envie-me as unidades da vossa lista de peças críticas e respondo com preço e prazo, para terem uma segunda fonte registada antes de precisarem.</t>
         </is>
       </c>
@@ -13518,7 +13518,7 @@
         <is>
           <t>Olá Dario,
 Na Sociedade Mineira de Catoca, os accionamentos dos britadores, lavadores e transportadores da lavaria são o que pára a produção quando um redutor falha.
-A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Envie-me as unidades da vossa lista de peças críticas e respondo com preço e prazo, para terem uma segunda fonte registada antes de precisarem.</t>
         </is>
       </c>
@@ -13621,7 +13621,7 @@
         <is>
           <t>Olá James,
 Na TechnipFMC, os accionamentos dos guinchos, gruas e equipamento de fabricação são o que pára a produção quando um redutor falha.
-A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Envie-me as unidades da vossa lista de peças críticas e respondo com preço e prazo, para terem uma segunda fonte registada antes de precisarem.</t>
         </is>
       </c>
@@ -13732,7 +13732,7 @@
         <is>
           <t>Olá Eugenia,
 Na TechnipFMC, os accionamentos dos guinchos, gruas e equipamento de fabricação são o que pára a produção quando um redutor falha.
-A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+A resposta habitual dos fornecedores é doze semanas. Temos em stock redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Envie-me as unidades da vossa lista de peças críticas e respondo com preço e prazo, para terem uma segunda fonte registada antes de precisarem.</t>
         </is>
       </c>
@@ -13839,7 +13839,7 @@
         <is>
           <t>Hi Seabi,
 At AECI Mining, the augers, mixers and conveyor drives on your emulsion plants are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -13950,7 +13950,7 @@
         <is>
           <t>Hi Tlamelo,
 At African Mining Services, the drivetrains and final drives across your contract fleet are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -14057,7 +14057,7 @@
         <is>
           <t>Hi Andries,
 At BME, a Member of the Omnia Group, the augers, mixers and pump drives on your emulsion and bulk explosives plants are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -14160,7 +14160,7 @@
         <is>
           <t>Hi Sidney,
 At Barminco, the drivetrains on your underground loaders and trucks are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -14271,7 +14271,7 @@
         <is>
           <t>Hi Modise,
 At Botswana Ash, the dredger, conveyor and crystalliser drives at Sua Pan are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -14374,7 +14374,7 @@
         <is>
           <t>Hi Obakeng,
 At Debswana Diamond Company, the crusher, scrubber and DMS plant drives, and the plant conveyors at Jwaneng and Orapa are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -14477,7 +14477,7 @@
         <is>
           <t>Hi Tebogo,
 At Debswana Diamond Company, the crusher, scrubber and DMS plant drives, and the plant conveyors at Jwaneng and Orapa are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -14584,7 +14584,7 @@
         <is>
           <t>Hi Adam,
 At Debswana Diamond Company, the crusher, scrubber and DMS plant drives, and the plant conveyors at Jwaneng and Orapa are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -14687,7 +14687,7 @@
         <is>
           <t>Hi Phemelo,
 At Debswana Diamond Company, the crusher, scrubber and DMS plant drives, and the plant conveyors at Jwaneng and Orapa are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -14790,7 +14790,7 @@
         <is>
           <t>Hi Badiri,
 Most gearbox spend sits with a single supplier on long lead times. That works until the unit is on backorder - and at Debswana Diamond Company that means the crusher, scrubber and DMS plant drives, and the plant conveyors at Jwaneng and Orapa.
-We supply [helical, bevel-helical and planetary] gearboxes and drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+We supply helical, bevel-helical and planetary gearboxes and drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 No switching required. Quote us against your current source and see where we land.
 What do you need from us for vendor registration?</t>
         </is>
@@ -14894,7 +14894,7 @@
         <is>
           <t>Hi Kago,
 At Debswana Diamond Company, the crusher, scrubber and DMS plant drives, and the plant conveyors at Jwaneng and Orapa are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -14997,7 +14997,7 @@
         <is>
           <t>Hi Gwere,
 At Debswana Diamond Company, the crusher, scrubber and DMS plant drives, and the plant conveyors at Jwaneng and Orapa are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -15100,7 +15100,7 @@
         <is>
           <t>Hi Keene,
 At Debswana Diamond Company, the crusher, scrubber and DMS plant drives, and the plant conveyors at Jwaneng and Orapa are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -15207,7 +15207,7 @@
         <is>
           <t>Hi Omphile,
 At Debswana Diamond Company, the crusher, scrubber and DMS plant drives, and the plant conveyors at Jwaneng and Orapa are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -15310,7 +15310,7 @@
         <is>
           <t>Hi Kevin,
 At Debswana Diamond Company, the crusher, scrubber and DMS plant drives, and the plant conveyors at Jwaneng and Orapa are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -15413,7 +15413,7 @@
         <is>
           <t>Hi Edwin,
 At Minergy Ltd, the crushing and screening plant drives at Masama are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -15516,7 +15516,7 @@
         <is>
           <t>Hi Mothusi,
 At Morupule Coal Mine, the coal conveyor, crusher and screen drives on the plant are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -15619,7 +15619,7 @@
         <is>
           <t>Hi Oaitse,
 At Morupule Coal Mine, the coal conveyor, crusher and screen drives on the plant are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -15722,7 +15722,7 @@
         <is>
           <t>Hi Kabo,
 At Morupule Coal Mine, the coal conveyor, crusher and screen drives on the plant are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -15829,7 +15829,7 @@
         <is>
           <t>Hi Onnete,
 At Sandfire, the mill and conveyor drives on the Motheo circuit are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -15940,7 +15940,7 @@
         <is>
           <t>Hi Teto,
 At Sandfire, the mill and conveyor drives on the Motheo circuit are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -16051,7 +16051,7 @@
         <is>
           <t>Hi Airborne,
 At UMS Group (United Mining Services), the winders, hoists and shaft equipment you install and maintain are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -16162,7 +16162,7 @@
         <is>
           <t>Hi Chimuka,
 At Barrick Mining Corporation, the mill and overland conveyor drives at Lumwana are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -16273,7 +16273,7 @@
         <is>
           <t>Hi Anton,
 At First Quantum Minerals, the SAG and ball mill drives, overland conveyors and crusher drives at Kansanshi and Sentinel are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -16384,7 +16384,7 @@
         <is>
           <t>Hi Theuns,
 At First Quantum Minerals, the SAG and ball mill drives, overland conveyors and crusher drives at Kansanshi and Sentinel are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -16491,7 +16491,7 @@
         <is>
           <t>Hi Sylvester,
 At First Quantum Minerals, the SAG and ball mill drives, overland conveyors and crusher drives at Kansanshi and Sentinel are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -16602,7 +16602,7 @@
         <is>
           <t>Hi Lutoba,
 At First Quantum Minerals, the SAG and ball mill drives, overland conveyors and crusher drives at Kansanshi and Sentinel are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -16713,7 +16713,7 @@
         <is>
           <t>Hi Ernest,
 At First Quantum Minerals, the SAG and ball mill drives, overland conveyors and crusher drives at Kansanshi and Sentinel are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -16824,7 +16824,7 @@
         <is>
           <t>Hi Wesley,
 At First Quantum Minerals, the SAG and ball mill drives, overland conveyors and crusher drives at Kansanshi and Sentinel are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -16935,7 +16935,7 @@
         <is>
           <t>Hi Mildred,
 At First Quantum Minerals, the SAG and ball mill drives, overland conveyors and crusher drives at Kansanshi and Sentinel are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -17042,7 +17042,7 @@
         <is>
           <t>Hi Jane,
 At First Quantum Minerals, the SAG and ball mill drives, overland conveyors and crusher drives at Kansanshi and Sentinel are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -17149,7 +17149,7 @@
         <is>
           <t>Hi Michael,
 At First Quantum Minerals, the SAG and ball mill drives, overland conveyors and crusher drives at Kansanshi and Sentinel are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -17256,7 +17256,7 @@
         <is>
           <t>Hi Dalitso,
 At First Quantum Minerals, the SAG and ball mill drives, overland conveyors and crusher drives at Kansanshi and Sentinel are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -17363,7 +17363,7 @@
         <is>
           <t>Hi Isaac,
 At First Quantum Minerals, the SAG and ball mill drives, overland conveyors and crusher drives at Kansanshi and Sentinel are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -17470,7 +17470,7 @@
         <is>
           <t>Hi Bright,
 At First Quantum Minerals, the SAG and ball mill drives, overland conveyors and crusher drives at Kansanshi and Sentinel are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -17581,7 +17581,7 @@
         <is>
           <t>Hi Vinod,
 At Konkola Copper Mines plc, the concentrator mill drives, shaft winders and tailings leach plant drives at Konkola and Nchanga are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -17684,7 +17684,7 @@
         <is>
           <t>Hi Laison,
 At Konkola Copper Mines plc, the concentrator mill drives, shaft winders and tailings leach plant drives at Konkola and Nchanga are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -17787,7 +17787,7 @@
         <is>
           <t>Hi Yoram,
 At Konkola Copper Mines plc, the concentrator mill drives, shaft winders and tailings leach plant drives at Konkola and Nchanga are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -17890,7 +17890,7 @@
         <is>
           <t>Hi Franklin,
 At Konkola Copper Mines plc, the concentrator mill drives, shaft winders and tailings leach plant drives at Konkola and Nchanga are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -17997,7 +17997,7 @@
         <is>
           <t>Hi Richard,
 At Konkola Copper Mines plc, the concentrator mill drives, shaft winders and tailings leach plant drives at Konkola and Nchanga are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -18104,7 +18104,7 @@
         <is>
           <t>Hi Mimosa,
 At Konkola Copper Mines plc, the concentrator mill drives, shaft winders and tailings leach plant drives at Konkola and Nchanga are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -18207,7 +18207,7 @@
         <is>
           <t>Hi Mutale,
 At Konkola Copper Mines plc, the concentrator mill drives, shaft winders and tailings leach plant drives at Konkola and Nchanga are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -18314,7 +18314,7 @@
         <is>
           <t>Hi Gregory,
 At Konkola Copper Mines plc, the concentrator mill drives, shaft winders and tailings leach plant drives at Konkola and Nchanga are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -18421,7 +18421,7 @@
         <is>
           <t>Hi Munalula,
 At Konkola Copper Mines plc, the concentrator mill drives, shaft winders and tailings leach plant drives at Konkola and Nchanga are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -18528,7 +18528,7 @@
         <is>
           <t>Hi Tozyani,
 At Mopani Copper Mines Plc, the shaft hoists, concentrator mills and smelter conveyor drives at Mufulira and Nkana are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -18631,7 +18631,7 @@
         <is>
           <t>Hi Philip,
 At Mopani Copper Mines Plc, the shaft hoists, concentrator mills and smelter conveyor drives at Mufulira and Nkana are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -18734,7 +18734,7 @@
         <is>
           <t>Hi Sabuni,
 At Mopani Copper Mines Plc, the shaft hoists, concentrator mills and smelter conveyor drives at Mufulira and Nkana are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -18833,7 +18833,7 @@
         <is>
           <t>Hi Gabriel,
 At Mopani Copper Mines Plc, the shaft hoists, concentrator mills and smelter conveyor drives at Mufulira and Nkana are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -18932,7 +18932,7 @@
         <is>
           <t>Hi Elijah,
 At Mopani Copper Mines Plc, the shaft hoists, concentrator mills and smelter conveyor drives at Mufulira and Nkana are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -19035,7 +19035,7 @@
         <is>
           <t>Hi George,
 At Mopani Copper Mines Plc, the shaft hoists, concentrator mills and smelter conveyor drives at Mufulira and Nkana are the units that stop production when a gearbox goes.
-The usual answer from suppliers is twelve weeks. We hold [helical, bevel-helical and planetary] gearboxes and supply drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+The usual answer from suppliers is twelve weeks. We hold helical, bevel-helical and planetary gearboxes, and supply drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 Send me the units on your critical spares list and I'll come back with price and lead time, so you have a second source on file before you need one.</t>
         </is>
       </c>
@@ -19138,7 +19138,7 @@
         <is>
           <t>Olá Malek,
 Fábricas como a BEFCO - Indústria compram peças de transmissão antes da campanha, não durante - os accionamentos dos misturadores, transportadores e linhas de produção custam muito mais a reparar em produção do que a ter em stock.
-Fornecemos redutores [helicoidais, cónicos, planetários e de eixo oco] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos, planetários e de eixo oco - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Se me indicar a data da próxima paragem, orçamento as unidades que deveriam estar em stock antes disso.</t>
         </is>
       </c>
@@ -19245,7 +19245,7 @@
         <is>
           <t>Olá Eduardo,
 Fábricas como a Carrinho Group compram peças de transmissão antes da campanha, não durante - os accionamentos dos moinhos, transportadores e linhas de enchimento custam muito mais a reparar em produção do que a ter em stock.
-Fornecemos redutores [helicoidais, cónicos, planetários e de eixo oco] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos, planetários e de eixo oco - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Se me indicar a data da próxima paragem, orçamento as unidades que deveriam estar em stock antes disso.</t>
         </is>
       </c>
@@ -19352,7 +19352,7 @@
         <is>
           <t>Olá Alessio,
 Fábricas como a Carrinho Group compram peças de transmissão antes da campanha, não durante - os accionamentos dos moinhos, transportadores e linhas de enchimento custam muito mais a reparar em produção do que a ter em stock.
-Fornecemos redutores [helicoidais, cónicos, planetários e de eixo oco] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos, planetários e de eixo oco - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Se me indicar a data da próxima paragem, orçamento as unidades que deveriam estar em stock antes disso.</t>
         </is>
       </c>
@@ -19459,7 +19459,7 @@
         <is>
           <t>Olá Pedro,
 Fábricas como a Carrinho Group compram peças de transmissão antes da campanha, não durante - os accionamentos dos moinhos, transportadores e linhas de enchimento custam muito mais a reparar em produção do que a ter em stock.
-Fornecemos redutores [helicoidais, cónicos, planetários e de eixo oco] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos, planetários e de eixo oco - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Se me indicar a data da próxima paragem, orçamento as unidades que deveriam estar em stock antes disso.</t>
         </is>
       </c>
@@ -19562,7 +19562,7 @@
         <is>
           <t>Olá Diego,
 Fábricas como a Castel Africa compram peças de transmissão antes da campanha, não durante - os accionamentos dos transportadores, enchedoras e linhas de embalagem custam muito mais a reparar em produção do que a ter em stock.
-Fornecemos redutores [helicoidais, cónicos, planetários e de eixo oco] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos, planetários e de eixo oco - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Se me indicar a data da próxima paragem, orçamento as unidades que deveriam estar em stock antes disso.</t>
         </is>
       </c>
@@ -19669,7 +19669,7 @@
         <is>
           <t>Olá Augusto,
 Grande parte da despesa em redutores concentra-se num único fornecedor com prazos longos. Funciona até a unidade estar em rutura - e na Castel Africa isso significa os accionamentos dos transportadores, enchedoras e linhas de embalagem.
-Fornecemos redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Não é preciso mudar de fornecedor: basta consultarem-nos como segunda fonte.
 O que precisam da nossa parte para o registo de fornecedor?</t>
         </is>
@@ -19777,7 +19777,7 @@
         <is>
           <t>Olá Ibrahim,
 Fábricas como a FOZKUDIA Industrial Lda compram peças de transmissão antes da campanha, não durante - os accionamentos dos misturadores, transportadores e linhas de produção custam muito mais a reparar em produção do que a ter em stock.
-Fornecemos redutores [helicoidais, cónicos, planetários e de eixo oco] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos, planetários e de eixo oco - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Se me indicar a data da próxima paragem, orçamento as unidades que deveriam estar em stock antes disso.</t>
         </is>
       </c>
@@ -19884,7 +19884,7 @@
         <is>
           <t>Olá Josemar,
 Fábricas como a MAXAM compram peças de transmissão antes da campanha, não durante - os accionamentos dos misturadores, sem-fins e transportadores da fábrica custam muito mais a reparar em produção do que a ter em stock.
-Fornecemos redutores [helicoidais, cónicos, planetários e de eixo oco] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos, planetários e de eixo oco - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Se me indicar a data da próxima paragem, orçamento as unidades que deveriam estar em stock antes disso.</t>
         </is>
       </c>
@@ -19995,7 +19995,7 @@
         <is>
           <t>Olá Pedro,
 Fábricas como a Nampak compram peças de transmissão antes da campanha, não durante - os accionamentos das prensas, transportadores e linhas de embalagem custam muito mais a reparar em produção do que a ter em stock.
-Fornecemos redutores [helicoidais, cónicos, planetários e de eixo oco] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos, planetários e de eixo oco - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Se me indicar a data da próxima paragem, orçamento as unidades que deveriam estar em stock antes disso.</t>
         </is>
       </c>
@@ -20106,7 +20106,7 @@
         <is>
           <t>Olá Gildo,
 Grande parte da despesa em redutores concentra-se num único fornecedor com prazos longos. Funciona até a unidade estar em rutura - e na Refriango isso significa os accionamentos dos transportadores, enchedoras e linhas de embalagem.
-Fornecemos redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Não é preciso mudar de fornecedor: basta consultarem-nos como segunda fonte.
 O que precisam da nossa parte para o registo de fornecedor?</t>
         </is>
@@ -20214,7 +20214,7 @@
         <is>
           <t>Olá Marcelino,
 Fábricas como a Siemens compram peças de transmissão antes da campanha, não durante - os redutores dos accionamentos e equipamentos que instalam e assistem custam muito mais a reparar em produção do que a ter em stock.
-Fornecemos redutores [helicoidais, cónicos, planetários e de eixo oco] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos, planetários e de eixo oco - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Se me indicar a data da próxima paragem, orçamento as unidades que deveriam estar em stock antes disso.</t>
         </is>
       </c>
@@ -20325,7 +20325,7 @@
         <is>
           <t>Olá Bruno,
 Fábricas como a Unique Beverages SA compram peças de transmissão antes da campanha, não durante - os accionamentos dos transportadores e da linha de enchimento custam muito mais a reparar em produção do que a ter em stock.
-Fornecemos redutores [helicoidais, cónicos, planetários e de eixo oco] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos, planetários e de eixo oco - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Se me indicar a data da próxima paragem, orçamento as unidades que deveriam estar em stock antes disso.</t>
         </is>
       </c>
@@ -20432,7 +20432,7 @@
         <is>
           <t>Olá Domingos,
 Fábricas como a Unotech, LDA compram peças de transmissão antes da campanha, não durante - os redutores dos equipamentos industriais que assistem custam muito mais a reparar em produção do que a ter em stock.
-Fornecemos redutores [helicoidais, cónicos, planetários e de eixo oco] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos, planetários e de eixo oco - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Se me indicar a data da próxima paragem, orçamento as unidades que deveriam estar em stock antes disso.</t>
         </is>
       </c>
@@ -20531,7 +20531,7 @@
         <is>
           <t>Olá Jose,
 Grande parte da despesa em redutores concentra-se num único fornecedor com prazos longos. Funciona até a unidade estar em rutura - e na Webcor Group isso significa os accionamentos dos moinhos de rolos, transportadores e elevadores de alcatruzes.
-Fornecemos redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Não é preciso mudar de fornecedor: basta consultarem-nos como segunda fonte.
 O que precisam da nossa parte para o registo de fornecedor?</t>
         </is>
@@ -20643,7 +20643,7 @@
         <is>
           <t>Olá Omran,
 Fábricas como a Webcor Group compram peças de transmissão antes da campanha, não durante - os accionamentos dos moinhos de rolos, transportadores e elevadores de alcatruzes custam muito mais a reparar em produção do que a ter em stock.
-Fornecemos redutores [helicoidais, cónicos, planetários e de eixo oco] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos, planetários e de eixo oco - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Se me indicar a data da próxima paragem, orçamento as unidades que deveriam estar em stock antes disso.</t>
         </is>
       </c>
@@ -20754,7 +20754,7 @@
         <is>
           <t>Olá Tatiana,
 Grande parte da despesa em redutores concentra-se num único fornecedor com prazos longos. Funciona até a unidade estar em rutura - e na Azule Energy isso significa os accionamentos dos guinchos, gruas e sistemas de amarração nas FPSO.
-Fornecemos redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Não é preciso mudar de fornecedor: basta consultarem-nos como segunda fonte.
 O que precisam da nossa parte para o registo de fornecedor?</t>
         </is>
@@ -20858,7 +20858,7 @@
         <is>
           <t>Olá Xavier,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na Azule Energy, isso significa os accionamentos dos guinchos, gruas e sistemas de amarração nas FPSO.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -20965,7 +20965,7 @@
         <is>
           <t>Olá Davide,
 Grande parte da despesa em redutores concentra-se num único fornecedor com prazos longos. Funciona até a unidade estar em rutura - e na Azule Energy isso significa os accionamentos dos guinchos, gruas e sistemas de amarração nas FPSO.
-Fornecemos redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Não é preciso mudar de fornecedor: basta consultarem-nos como segunda fonte.
 O que precisam da nossa parte para o registo de fornecedor?</t>
         </is>
@@ -21073,7 +21073,7 @@
         <is>
           <t>Olá Nivaldo,
 Grande parte da despesa em redutores concentra-se num único fornecedor com prazos longos. Funciona até a unidade estar em rutura - e na Azule Energy isso significa os accionamentos dos guinchos, gruas e sistemas de amarração nas FPSO.
-Fornecemos redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Não é preciso mudar de fornecedor: basta consultarem-nos como segunda fonte.
 O que precisam da nossa parte para o registo de fornecedor?</t>
         </is>
@@ -21181,7 +21181,7 @@
         <is>
           <t>Olá Cipriano,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na Azule Energy, isso significa os accionamentos dos guinchos, gruas e sistemas de amarração nas FPSO.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -21288,7 +21288,7 @@
         <is>
           <t>Olá Dionisio,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na CONSUL-MARINE, isso significa os redutores dos guinchos, cabrestantes e accionamentos marítimos.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -21395,7 +21395,7 @@
         <is>
           <t>Olá Stuart,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na Chevron, isso significa os accionamentos dos guinchos, gruas e equipamento rotativo offshore.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -21506,7 +21506,7 @@
         <is>
           <t>Olá Claudio,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na Core Laboratories, isso significa os redutores dos equipamentos de campo e laboratório.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -21617,7 +21617,7 @@
         <is>
           <t>Olá Mohamed,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na Core Laboratories, isso significa os redutores dos equipamentos de campo e laboratório.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -21728,7 +21728,7 @@
         <is>
           <t>Olá Juelson,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na Core Laboratories, isso significa os redutores dos equipamentos de campo e laboratório.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -21839,7 +21839,7 @@
         <is>
           <t>Olá Erlend,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na DOF, isso significa os redutores dos guinchos, cabrestantes e propulsores das embarcações.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -21946,7 +21946,7 @@
         <is>
           <t>Olá Adao,
 Grande parte da despesa em redutores concentra-se num único fornecedor com prazos longos. Funciona até a unidade estar em rutura - e na ExxonMobil isso significa os accionamentos dos guinchos, gruas e equipamento rotativo offshore.
-Fornecemos redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Não é preciso mudar de fornecedor: basta consultarem-nos como segunda fonte.
 O que precisam da nossa parte para o registo de fornecedor?</t>
         </is>
@@ -22054,7 +22054,7 @@
         <is>
           <t>Olá Mario,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na OCEANBIZZ, isso significa os redutores dos guinchos e accionamentos marítimos.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -22161,7 +22161,7 @@
         <is>
           <t>Olá Giuseppe,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na PETROBEL, isso significa os accionamentos dos guinchos e equipamento rotativo em terra.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -22268,7 +22268,7 @@
         <is>
           <t>Olá Kelson,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na PWSIX LDA, isso significa os redutores dos equipamentos que operam em campo.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -22367,7 +22367,7 @@
         <is>
           <t>Olá Igor,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na Perbras, isso significa os redutores dos guinchos e equipamento rotativo de campo.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -22470,7 +22470,7 @@
         <is>
           <t>Olá Francisco,
 Grande parte da despesa em redutores concentra-se num único fornecedor com prazos longos. Funciona até a unidade estar em rutura - e na Petromar Lda isso significa os accionamentos dos guinchos, gruas e equipamento de fabricação.
-Fornecemos redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Não é preciso mudar de fornecedor: basta consultarem-nos como segunda fonte.
 O que precisam da nossa parte para o registo de fornecedor?</t>
         </is>
@@ -22570,7 +22570,7 @@
         <is>
           <t>Olá Nembamba,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na Puma Energy, isso significa os accionamentos das bombas e equipamento de movimentação nos terminais.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -22681,7 +22681,7 @@
         <is>
           <t>Olá Lidia,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na Pumangol, isso significa os accionamentos das bombas e equipamento de movimentação nos terminais.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -22784,7 +22784,7 @@
         <is>
           <t>Olá Carlos,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na SONILS - Sonangol Integrated Logistics Services, isso significa os accionamentos das gruas, pórtico e equipamento de movimentação da base.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -22887,7 +22887,7 @@
         <is>
           <t>Olá Tomas,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na Siemens Energy, isso significa os redutores das turbinas, geradores e accionamentos auxiliares.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -22998,7 +22998,7 @@
         <is>
           <t>Olá Nuno,
 Grande parte da despesa em redutores concentra-se num único fornecedor com prazos longos. Funciona até a unidade estar em rutura - e na TechnipFMC isso significa os accionamentos dos guinchos, gruas e equipamento de fabricação.
-Fornecemos redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Não é preciso mudar de fornecedor: basta consultarem-nos como segunda fonte.
 O que precisam da nossa parte para o registo de fornecedor?</t>
         </is>
@@ -23106,7 +23106,7 @@
         <is>
           <t>Olá Carlos,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na TotalEnergies, isso significa os accionamentos dos guinchos, gruas e equipamento rotativo offshore.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -23213,7 +23213,7 @@
         <is>
           <t>Olá Afonso,
 Grande parte da despesa em redutores concentra-se num único fornecedor com prazos longos. Funciona até a unidade estar em rutura - e na TotalEnergies isso significa os accionamentos dos guinchos, gruas e equipamento rotativo offshore.
-Fornecemos redutores [helicoidais, cónicos e planetários] e substituições compatíveis com [SEW, Flender, David Brown] - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores helicoidais, cónicos e planetários, e substituições compatíveis com SEW-Eurodrive, Flender, Bonfiglioli e David Brown - 10 a 14 dias até Angola para as medidas em stock, 4 a 6 semanas por encomenda, com recondicionamento por troca.
 Não é preciso mudar de fornecedor: basta consultarem-nos como segunda fonte.
 O que precisam da nossa parte para o registo de fornecedor?</t>
         </is>
@@ -23321,7 +23321,7 @@
         <is>
           <t>Olá Elinisa,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na TotalEnergies, isso significa os accionamentos dos guinchos, gruas e equipamento rotativo offshore.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -23432,7 +23432,7 @@
         <is>
           <t>Olá Adil,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na TotalEnergies, isso significa os accionamentos dos guinchos, gruas e equipamento rotativo offshore.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -23543,7 +23543,7 @@
         <is>
           <t>Olá Emil,
 Em operações offshore e portuárias o equipamento costuma estar disponível - o redutor é que não está. Na Victory Oil &amp; Energy, isso significa os redutores dos guinchos e equipamento de intervenção em poço.
-Fornecemos redutores [industriais, de eixo oco e marítimos], guinchos e accionamentos - [X] dias até Angola, com recondicionamento por troca.
+Fornecemos redutores industriais, de eixo oco e marítimos, guinchos e accionamentos - 10 a 14 dias até Angola para as medidas em stock, com recondicionamento por troca.
 Envie-me os accionamentos que mais problemas dão e respondo com preço e prazo. Se não formos melhores que a vossa fonte actual, não perdeu nada.</t>
         </is>
       </c>
@@ -23642,7 +23642,7 @@
         <is>
           <t>Hi Mpaphi,
 Plants like Botswana Meat Commission buy drive spares before the season, not during it - the conveyor, rendering and processing line drives in the abattoir cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Botswana, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Botswana for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -23745,7 +23745,7 @@
         <is>
           <t>Hi Carl,
 Plants like Botswana Meat Commission buy drive spares before the season, not during it - the conveyor, rendering and processing line drives in the abattoir cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Botswana, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Botswana for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -23848,7 +23848,7 @@
         <is>
           <t>Hi Othusitse,
 Plants like Botswana Meat Commission buy drive spares before the season, not during it - the conveyor, rendering and processing line drives in the abattoir cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Botswana, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Botswana for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -23955,7 +23955,7 @@
         <is>
           <t>Hi Onalenna,
 Most gearbox spend sits with a single supplier on long lead times. That works until the unit is on backorder - and at Coca-Cola Beverages Africa that means the conveyor, filler and packing line drives on the bottling hall.
-We supply [helical, bevel-helical and planetary] gearboxes and drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+We supply helical, bevel-helical and planetary gearboxes and drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 No switching required. Quote us against your current source and see where we land.
 What do you need from us for vendor registration?</t>
         </is>
@@ -24063,7 +24063,7 @@
         <is>
           <t>Hi Tlhabologang,
 Most gearbox spend sits with a single supplier on long lead times. That works until the unit is on backorder - and at Irvine's Group that means the feed mill, conveyor and processing line drives.
-We supply [helical, bevel-helical and planetary] gearboxes and drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+We supply helical, bevel-helical and planetary gearboxes and drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 No switching required. Quote us against your current source and see where we land.
 What do you need from us for vendor registration?</t>
         </is>
@@ -24167,7 +24167,7 @@
         <is>
           <t>Hi Mothobi,
 Plants like Lactalis Group buy drive spares before the season, not during it - the homogeniser, conveyor and packing line drives on the dairy cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Botswana, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Botswana for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -24274,7 +24274,7 @@
         <is>
           <t>Hi Kago,
 Most gearbox spend sits with a single supplier on long lead times. That works until the unit is on backorder - and at PepsiCo that means the conveyor, filler and packing line drives on the bottling hall.
-We supply [helical, bevel-helical and planetary] gearboxes and drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+We supply helical, bevel-helical and planetary gearboxes and drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 No switching required. Quote us against your current source and see where we land.
 What do you need from us for vendor registration?</t>
         </is>
@@ -24386,7 +24386,7 @@
         <is>
           <t>Hi Otlhokilwe,
 Plants like Saint-Gobain buy drive spares before the season, not during it - the mixer, conveyor and press drives on the plant cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Botswana, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Botswana for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -24493,7 +24493,7 @@
         <is>
           <t>Hi Engmogomotsi,
 At BOTSWANA POWER CORPORATION, the coal handling conveyor, mill and ash plant drives at Morupule fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Botswana, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Botswana for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -24596,7 +24596,7 @@
         <is>
           <t>Hi Thuso,
 At BOTSWANA POWER CORPORATION, the coal handling conveyor, mill and ash plant drives at Morupule fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Botswana, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Botswana for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -24703,7 +24703,7 @@
         <is>
           <t>Hi Tshidiso,
 At Barloworld Equipment, the final drives and transmissions on the machines you support fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Botswana, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Botswana for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -24810,7 +24810,7 @@
         <is>
           <t>Hi Khotso,
 At Barloworld Equipment, the final drives and transmissions on the machines you support fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Botswana, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Botswana for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -24917,7 +24917,7 @@
         <is>
           <t>Hi Noboth,
 At Lucient Engineering and Construction (Pty) Ltd, the gearboxes on the plant and equipment you run on site fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Botswana, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Botswana for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -25020,7 +25020,7 @@
         <is>
           <t>Hi Donald,
 At Pacific Logistics, the drivetrain and materials handling drives across the fleet fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Botswana, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Botswana for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -25127,7 +25127,7 @@
         <is>
           <t>Hi Molebedi,
 At Puma Energy Botswana Pty. Ltd., the pump and handling drives at the terminals and depots fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Botswana, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Botswana for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -25226,7 +25226,7 @@
         <is>
           <t>Hi Idah,
 Most gearbox spend sits with a single supplier on long lead times. That works until the unit is on backorder - and at Vivo Energy that means the pump, loading arm and handling drives at the terminals.
-We supply [helical, bevel-helical and planetary] gearboxes and drop-in replacements for [SEW, Flender, David Brown] - [X] days into Botswana, with rebuild-on-exchange.
+We supply helical, bevel-helical and planetary gearboxes and drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Botswana for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 No switching required. Quote us against your current source and see where we land.
 What do you need from us for vendor registration?</t>
         </is>
@@ -25334,7 +25334,7 @@
         <is>
           <t>Hi Rahul,
 Plants like 260 Brands buy drive spares before the season, not during it - the mixer, conveyor and packing line drives on the plant cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -25437,7 +25437,7 @@
         <is>
           <t>Hi Innocent,
 Plants like Advanta Seeds buy drive spares before the season, not during it - the seed processing, grading and conveyor drives on the plant cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -25544,7 +25544,7 @@
         <is>
           <t>Hi Brian,
 Plants like Austin Powder buy drive spares before the season, not during it - the mixers, augers and conveyor drives on your plant cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -25651,7 +25651,7 @@
         <is>
           <t>Hi Chanda,
 Plants like Cargill buy drive spares before the season, not during it - the mill, conveyor and elevator drives on the processing line cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -25762,7 +25762,7 @@
         <is>
           <t>Hi Patson,
 Plants like Chilanga Cement Plc buy drive spares before the season, not during it - the raw mill, kiln and cement mill drives, and the clinker conveyors cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -25861,7 +25861,7 @@
         <is>
           <t>Hi Nason,
 Plants like Dangote Industries Limited buy drive spares before the season, not during it - the raw mill, kiln and cement mill drives, and the plant conveyors cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -25972,7 +25972,7 @@
         <is>
           <t>Hi Hitesh,
 Most gearbox spend sits with a single supplier on long lead times. That works until the unit is on backorder - and at Estim Construction Co. Ltd. that means the batching plant, crusher and conveyor drives on site.
-We supply [helical, bevel-helical and planetary] gearboxes and drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical and planetary gearboxes and drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 No switching required. Quote us against your current source and see where we land.
 What do you need from us for vendor registration?</t>
         </is>
@@ -26080,7 +26080,7 @@
         <is>
           <t>Hi Michael,
 Plants like Good Nature Agro buy drive spares before the season, not during it - the seed cleaning, grading and conveyor drives on the plant cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -26183,7 +26183,7 @@
         <is>
           <t>Hi Ranjeet,
 Plants like Mount Meru Group buy drive spares before the season, not during it - the expeller, conveyor and refinery drives on the oil plant cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -26294,7 +26294,7 @@
         <is>
           <t>Hi Gabriel,
 Most gearbox spend sits with a single supplier on long lead times. That works until the unit is on backorder - and at National Milling Corporation Limited that means the roller mill, conveyor and bucket elevator drives on the mill.
-We supply [helical, bevel-helical and planetary] gearboxes and drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical and planetary gearboxes and drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 No switching required. Quote us against your current source and see where we land.
 What do you need from us for vendor registration?</t>
         </is>
@@ -26394,7 +26394,7 @@
         <is>
           <t>Hi Sulan,
 Most gearbox spend sits with a single supplier on long lead times. That works until the unit is on backorder - and at National Milling Corporation Limited that means the roller mill, conveyor and bucket elevator drives on the mill.
-We supply [helical, bevel-helical and planetary] gearboxes and drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical and planetary gearboxes and drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 No switching required. Quote us against your current source and see where we land.
 What do you need from us for vendor registration?</t>
         </is>
@@ -26494,7 +26494,7 @@
         <is>
           <t>Hi Gideon,
 Plants like National Milling Corporation Limited buy drive spares before the season, not during it - the roller mill, conveyor and bucket elevator drives on the mill cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -26597,7 +26597,7 @@
         <is>
           <t>Hi Milton,
 Plants like Olam buy drive spares before the season, not during it - the mill, conveyor and elevator drives on the processing line cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -26704,7 +26704,7 @@
         <is>
           <t>Hi Robert,
 Plants like Royal De Heus buy drive spares before the season, not during it - the hammer mill, pellet mill and conveyor drives on the feed mill cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -26815,7 +26815,7 @@
         <is>
           <t>Hi Mwendo,
 Plants like Synergy Seeds Zambia buy drive spares before the season, not during it - the seed cleaner, grader and conveyor drives on the plant cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -26918,7 +26918,7 @@
         <is>
           <t>Hi James,
 Plants like TATA Zambia buy drive spares before the season, not during it - the gearboxes on the plant and vehicles you run cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -27025,7 +27025,7 @@
         <is>
           <t>Hi Jones,
 Plants like Trade Kings Group buy drive spares before the season, not during it - the mixer, conveyor and packing line drives across the plant cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -27128,7 +27128,7 @@
         <is>
           <t>Hi Chanda,
 Most gearbox spend sits with a single supplier on long lead times. That works until the unit is on backorder - and at VARUN BEVERAGES LIMITED that means the conveyor, filler and packing line drives on the bottling hall.
-We supply [helical, bevel-helical and planetary] gearboxes and drop-in replacements for [SEW, Flender, David Brown] - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical and planetary gearboxes and drop-in replacements for SEW-Eurodrive, Flender, Bonfiglioli and David Brown - 10 to 14 days into Zambia for stocked sizes, 4 to 6 weeks made to order, with rebuild-on-exchange.
 No switching required. Quote us against your current source and see where we land.
 What do you need from us for vendor registration?</t>
         </is>
@@ -27236,7 +27236,7 @@
         <is>
           <t>Hi Roger,
 Plants like Yoyo Foods buy drive spares before the season, not during it - the mixer, conveyor and packing line drives on the plant cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -27335,7 +27335,7 @@
         <is>
           <t>Hi Mohammed,
 Plants like Yoyo Foods buy drive spares before the season, not during it - the mixer, conveyor and packing line drives on the plant cost far more to fix mid-run than to hold on the shelf.
-We supply [helical, bevel-helical, planetary and shaft-mounted] gearboxes - [X] days into Zambia, with rebuild-on-exchange.
+We supply helical, bevel-helical, planetary and shaft-mounted gearboxes - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 If you tell me roughly when your next shutdown falls, I'll quote the units worth having in stock before it.</t>
         </is>
       </c>
@@ -27438,7 +27438,7 @@
         <is>
           <t>Hi Mwila,
 At Africa Global Logistics, the materials handling, crane and conveyor drives at the terminals fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Zambia, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -27541,7 +27541,7 @@
         <is>
           <t>Hi Johannes,
 At BIA GROUP, the final drives, travel and swing drives on the machines you support fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Zambia, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -27648,7 +27648,7 @@
         <is>
           <t>Hi Kenneth,
 At Barloworld Equipment, the final drives and transmissions on the machines you support fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Zambia, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -27755,7 +27755,7 @@
         <is>
           <t>Hi Owen,
 At Copperbelt Energy Corporation Plc, the auxiliary and handling drives across the network fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Zambia, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -27858,7 +27858,7 @@
         <is>
           <t>Hi Busiku,
 At Ignite Energy Access, the gearboxes on the pumping and milling equipment you deploy fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Zambia, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -27961,7 +27961,7 @@
         <is>
           <t>Hi Kingsley,
 At Juba Transport Limited, the drivetrain, PTO and winch gearboxes across the fleet fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Zambia, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -28068,7 +28068,7 @@
         <is>
           <t>Hi Yogen,
 At Lake Oil Group, the pump, drivetrain and handling drives across the fleet and depots fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Zambia, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -28179,7 +28179,7 @@
         <is>
           <t>Hi Michael,
 At SABOT Group, the drivetrain, PTO and winch gearboxes across the fleet fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Zambia, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -28286,7 +28286,7 @@
         <is>
           <t>Hi Patrick,
 At Simba Group, the drivetrain and materials handling drives across the fleet fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Zambia, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -28389,7 +28389,7 @@
         <is>
           <t>Hi Gregory,
 At Vivo Energy, the pump, loading arm and handling drives at the terminals fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Zambia, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -28496,7 +28496,7 @@
         <is>
           <t>Hi Vernon,
 At Vivo Energy, the pump, loading arm and handling drives at the terminals fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Zambia, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -28603,7 +28603,7 @@
         <is>
           <t>Hi Agripa,
 At ZESCO, the gate, crane and auxiliary drives on the hydro stations fail the same way everywhere: the machine is available, the gearbox is not.
-We supply [industrial, shaft-mounted and mobile] gearboxes plus travel and swing drives - [X] days into Zambia, with rebuild-on-exchange.
+We supply industrial, shaft-mounted and mobile gearboxes plus travel and swing drives - 10 to 14 days into Zambia for stocked sizes, with rebuild-on-exchange.
 Send me the drives that give you the most trouble and I'll come back with price and lead time. If we are not better than your current source, nothing lost.</t>
         </is>
       </c>
@@ -28676,7 +28676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A45"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="108" customWidth="1" min="1" max="1"/>
@@ -28781,181 +28781,202 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Before you send: replace every [BRACKET] with your own details - product range, lead time in</t>
+          <t>Check these two numbers before you send - I filled them with industry-standard values, not</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>days, and the OEM brands you can replace. I do not know those, so I left them blank rather</t>
+          <t>with your actual terms:</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>than invent them. No signature is included; you add your own.</t>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Lead time: '10 to 14 days for stocked sizes, 4 to 6 weeks made to order'.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr"/>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Brands replaced: SEW-Eurodrive, Flender, Bonfiglioli, David Brown.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="42" t="inlineStr">
-        <is>
-          <t>How to work it</t>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>If either is wrong for you, find-and-replace it across column K before sending. Everything</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
+          <t>else is ready as written. No signature is included; you add your own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="42" t="inlineStr">
+        <is>
+          <t>How to work it</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
           <t>1. Tier A first - the 46 distributors and dealers. They resell and stock, so they buy repeatedly.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>2. Then Tier B - mining. Highest spend; a stopped mill drive costs them thousands per hour.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>3. Tier C last - agro, cement, energy, logistics.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="42" t="inlineStr">
-        <is>
-          <t>Which cells you fill in</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
+          <t>3. Tier C last - agro, cement, energy, logistics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="42" t="inlineStr">
+        <is>
+          <t>Which cells you fill in</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
           <t>The four yellow columns on the Leads tab: Status, Date sent, Replied, Notes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Everything left of them is source data. Leave it alone so the Summary tab stays correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="42" t="inlineStr">
-        <is>
-          <t>Deliverability - please read</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
+          <t>Everything left of them is source data. Leave it alone so the Summary tab stays correct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="42" t="inlineStr">
+        <is>
+          <t>Deliverability - please read</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
           <t>Contacts per company were capped on purpose. First Quantum has hundreds of matching engineers;</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>emailing all of them from a cold domain gets your domain flagged as spam and kills the batch.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>Warm the sending domain up first and keep daily volume low for the first two weeks.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="42" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="42" t="inlineStr">
         <is>
           <t>Known gaps</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Tshegofatso Mosweu is listed in Botswana but his employer SPTC is a Saudi transformer maker.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Verify that one before sending.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>The 'Check' column flags contacts whose employer is headquartered abroad - confirm they buy</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>locally rather than through a regional office. Context for the call, not a reason to drop them.</t>
+          <t>Tshegofatso Mosweu is listed in Botswana but his employer SPTC is a Saudi transformer maker.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>No phone numbers in this batch, by request.</t>
+          <t>Verify that one before sending.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr"/>
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>The 'Check' column flags contacts whose employer is headquartered abroad - confirm they buy</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="42" t="inlineStr">
-        <is>
-          <t>Next batches</t>
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>locally rather than through a regional office. Context for the call, not a reason to drop them.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
+          <t>No phone numbers in this batch, by request.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="42" t="inlineStr">
+        <is>
+          <t>Next batches</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Batch 2 - remaining mining and energy depth in all three countries</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   Batch 3 - second and third contacts at accounts that engage in batch 1</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   Batch 4 - Namibia, DRC Copperbelt, Mozambique, Zimbabwe</t>
         </is>

--- a/campaigns/gearbox-southern-africa/Gearbox-Leads-v3-EMAILS-PER-COMPANY.xlsx
+++ b/campaigns/gearbox-southern-africa/Gearbox-Leads-v3-EMAILS-PER-COMPANY.xlsx
@@ -22,8 +22,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -190,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -216,7 +216,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -285,7 +285,7 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -313,6 +313,12 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -722,7 +728,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -786,7 +791,6 @@
         <v/>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -894,7 +898,6 @@
         <v/>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
@@ -978,7 +981,6 @@
         <v/>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
@@ -1027,7 +1029,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
@@ -1141,12 +1142,11 @@
           <t>Reply rate</t>
         </is>
       </c>
-      <c r="B45" s="13">
+      <c r="B45" s="46">
         <f>IFERROR(COUNTIF(Leads!$W$2:$W$201,"Replied")/MAX(1,COUNTIF(Leads!$W$2:$W$201,"Emailed")+COUNTIF(Leads!$W$2:$W$201,"Follow-up sent")+COUNTIF(Leads!$W$2:$W$201,"Replied")),0)</f>
         <v/>
       </c>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X2" s="36" t="n"/>
+      <c r="X2" s="47" t="n"/>
       <c r="Y2" s="35" t="n"/>
       <c r="Z2" s="37" t="n"/>
     </row>
@@ -9195,7 +9195,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X3" s="36" t="n"/>
+      <c r="X3" s="47" t="n"/>
       <c r="Y3" s="35" t="n"/>
       <c r="Z3" s="37" t="n"/>
     </row>
@@ -9310,7 +9310,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X4" s="36" t="n"/>
+      <c r="X4" s="47" t="n"/>
       <c r="Y4" s="35" t="n"/>
       <c r="Z4" s="37" t="n"/>
     </row>
@@ -9421,7 +9421,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X5" s="36" t="n"/>
+      <c r="X5" s="47" t="n"/>
       <c r="Y5" s="35" t="n"/>
       <c r="Z5" s="37" t="n"/>
     </row>
@@ -9536,7 +9536,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X6" s="36" t="n"/>
+      <c r="X6" s="47" t="n"/>
       <c r="Y6" s="35" t="n"/>
       <c r="Z6" s="37" t="n"/>
     </row>
@@ -9651,7 +9651,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X7" s="36" t="n"/>
+      <c r="X7" s="47" t="n"/>
       <c r="Y7" s="35" t="n"/>
       <c r="Z7" s="37" t="n"/>
     </row>
@@ -9762,7 +9762,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X8" s="36" t="n"/>
+      <c r="X8" s="47" t="n"/>
       <c r="Y8" s="35" t="n"/>
       <c r="Z8" s="37" t="n"/>
     </row>
@@ -9873,7 +9873,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X9" s="36" t="n"/>
+      <c r="X9" s="47" t="n"/>
       <c r="Y9" s="35" t="n"/>
       <c r="Z9" s="37" t="n"/>
     </row>
@@ -9984,7 +9984,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X10" s="36" t="n"/>
+      <c r="X10" s="47" t="n"/>
       <c r="Y10" s="35" t="n"/>
       <c r="Z10" s="37" t="n"/>
     </row>
@@ -10103,7 +10103,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X11" s="36" t="n"/>
+      <c r="X11" s="47" t="n"/>
       <c r="Y11" s="35" t="n"/>
       <c r="Z11" s="37" t="n"/>
     </row>
@@ -10226,7 +10226,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X12" s="36" t="n"/>
+      <c r="X12" s="47" t="n"/>
       <c r="Y12" s="35" t="n"/>
       <c r="Z12" s="37" t="n"/>
     </row>
@@ -10333,7 +10333,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X13" s="36" t="n"/>
+      <c r="X13" s="47" t="n"/>
       <c r="Y13" s="35" t="n"/>
       <c r="Z13" s="37" t="n"/>
     </row>
@@ -10452,7 +10452,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X14" s="36" t="n"/>
+      <c r="X14" s="47" t="n"/>
       <c r="Y14" s="35" t="n"/>
       <c r="Z14" s="37" t="n"/>
     </row>
@@ -10567,7 +10567,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X15" s="36" t="n"/>
+      <c r="X15" s="47" t="n"/>
       <c r="Y15" s="35" t="n"/>
       <c r="Z15" s="37" t="n"/>
     </row>
@@ -10682,7 +10682,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X16" s="36" t="n"/>
+      <c r="X16" s="47" t="n"/>
       <c r="Y16" s="35" t="n"/>
       <c r="Z16" s="37" t="n"/>
     </row>
@@ -10801,7 +10801,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X17" s="36" t="n"/>
+      <c r="X17" s="47" t="n"/>
       <c r="Y17" s="35" t="n"/>
       <c r="Z17" s="37" t="n"/>
     </row>
@@ -10916,7 +10916,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X18" s="36" t="n"/>
+      <c r="X18" s="47" t="n"/>
       <c r="Y18" s="35" t="n"/>
       <c r="Z18" s="37" t="n"/>
     </row>
@@ -11031,7 +11031,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X19" s="36" t="n"/>
+      <c r="X19" s="47" t="n"/>
       <c r="Y19" s="35" t="n"/>
       <c r="Z19" s="37" t="n"/>
     </row>
@@ -11146,7 +11146,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X20" s="36" t="n"/>
+      <c r="X20" s="47" t="n"/>
       <c r="Y20" s="35" t="n"/>
       <c r="Z20" s="37" t="n"/>
     </row>
@@ -11261,7 +11261,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X21" s="36" t="n"/>
+      <c r="X21" s="47" t="n"/>
       <c r="Y21" s="35" t="n"/>
       <c r="Z21" s="37" t="n"/>
     </row>
@@ -11368,7 +11368,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X22" s="36" t="n"/>
+      <c r="X22" s="47" t="n"/>
       <c r="Y22" s="35" t="n"/>
       <c r="Z22" s="37" t="n"/>
     </row>
@@ -11479,7 +11479,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X23" s="36" t="n"/>
+      <c r="X23" s="47" t="n"/>
       <c r="Y23" s="35" t="n"/>
       <c r="Z23" s="37" t="n"/>
     </row>
@@ -11590,7 +11590,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X24" s="36" t="n"/>
+      <c r="X24" s="47" t="n"/>
       <c r="Y24" s="35" t="n"/>
       <c r="Z24" s="37" t="n"/>
     </row>
@@ -11709,7 +11709,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X25" s="36" t="n"/>
+      <c r="X25" s="47" t="n"/>
       <c r="Y25" s="35" t="n"/>
       <c r="Z25" s="37" t="n"/>
     </row>
@@ -11824,7 +11824,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X26" s="36" t="n"/>
+      <c r="X26" s="47" t="n"/>
       <c r="Y26" s="35" t="n"/>
       <c r="Z26" s="37" t="n"/>
     </row>
@@ -11928,12 +11928,18 @@
       <c r="V27" s="19" t="inlineStr"/>
       <c r="W27" s="35" t="inlineStr">
         <is>
-          <t>Not contacted</t>
-        </is>
-      </c>
-      <c r="X27" s="36" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="X27" s="47" t="n">
+        <v>46232</v>
+      </c>
       <c r="Y27" s="35" t="n"/>
-      <c r="Z27" s="37" t="n"/>
+      <c r="Z27" s="37" t="inlineStr">
+        <is>
+          <t>Sent 29-Jul-2026 07:53 from Outlook, cc Haffar, Kayacan, Nesren. Delivered, no bounce.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="27" t="inlineStr">
@@ -12035,12 +12041,18 @@
       <c r="V28" s="24" t="inlineStr"/>
       <c r="W28" s="35" t="inlineStr">
         <is>
-          <t>Not contacted</t>
-        </is>
-      </c>
-      <c r="X28" s="36" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="X28" s="47" t="n">
+        <v>46232</v>
+      </c>
       <c r="Y28" s="35" t="n"/>
-      <c r="Z28" s="37" t="n"/>
+      <c r="Z28" s="37" t="inlineStr">
+        <is>
+          <t>Sent 29-Jul-2026 07:56 from Outlook, cc Haffar, Kayacan, Nesren, Tahir. Delivered, no bounce.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="38" t="inlineStr">
@@ -12157,7 +12169,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X29" s="36" t="n"/>
+      <c r="X29" s="47" t="n"/>
       <c r="Y29" s="35" t="n"/>
       <c r="Z29" s="37" t="n"/>
     </row>
@@ -12264,7 +12276,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X30" s="36" t="n"/>
+      <c r="X30" s="47" t="n"/>
       <c r="Y30" s="35" t="n"/>
       <c r="Z30" s="37" t="n"/>
     </row>
@@ -12379,7 +12391,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X31" s="36" t="n"/>
+      <c r="X31" s="47" t="n"/>
       <c r="Y31" s="35" t="n"/>
       <c r="Z31" s="37" t="n"/>
     </row>
@@ -12498,7 +12510,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X32" s="36" t="n"/>
+      <c r="X32" s="47" t="n"/>
       <c r="Y32" s="35" t="n"/>
       <c r="Z32" s="37" t="n"/>
     </row>
@@ -12605,7 +12617,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X33" s="36" t="n"/>
+      <c r="X33" s="47" t="n"/>
       <c r="Y33" s="35" t="n"/>
       <c r="Z33" s="37" t="n"/>
     </row>
@@ -12720,7 +12732,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X34" s="36" t="n"/>
+      <c r="X34" s="47" t="n"/>
       <c r="Y34" s="35" t="n"/>
       <c r="Z34" s="37" t="n"/>
     </row>
@@ -12827,7 +12839,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X35" s="36" t="n"/>
+      <c r="X35" s="47" t="n"/>
       <c r="Y35" s="35" t="n"/>
       <c r="Z35" s="37" t="n"/>
     </row>
@@ -12942,7 +12954,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X36" s="36" t="n"/>
+      <c r="X36" s="47" t="n"/>
       <c r="Y36" s="35" t="n"/>
       <c r="Z36" s="37" t="n"/>
     </row>
@@ -13057,7 +13069,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X37" s="36" t="n"/>
+      <c r="X37" s="47" t="n"/>
       <c r="Y37" s="35" t="n"/>
       <c r="Z37" s="37" t="n"/>
     </row>
@@ -13172,7 +13184,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X38" s="36" t="n"/>
+      <c r="X38" s="47" t="n"/>
       <c r="Y38" s="35" t="n"/>
       <c r="Z38" s="37" t="n"/>
     </row>
@@ -13283,7 +13295,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X39" s="36" t="n"/>
+      <c r="X39" s="47" t="n"/>
       <c r="Y39" s="35" t="n"/>
       <c r="Z39" s="37" t="n"/>
     </row>
@@ -13390,7 +13402,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X40" s="36" t="n"/>
+      <c r="X40" s="47" t="n"/>
       <c r="Y40" s="35" t="n"/>
       <c r="Z40" s="37" t="n"/>
     </row>
@@ -13501,7 +13513,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X41" s="36" t="n"/>
+      <c r="X41" s="47" t="n"/>
       <c r="Y41" s="35" t="n"/>
       <c r="Z41" s="37" t="n"/>
     </row>
@@ -13608,7 +13620,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X42" s="36" t="n"/>
+      <c r="X42" s="47" t="n"/>
       <c r="Y42" s="35" t="n"/>
       <c r="Z42" s="37" t="n"/>
     </row>
@@ -13723,7 +13735,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X43" s="36" t="n"/>
+      <c r="X43" s="47" t="n"/>
       <c r="Y43" s="35" t="n"/>
       <c r="Z43" s="37" t="n"/>
     </row>
@@ -13838,7 +13850,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X44" s="36" t="n"/>
+      <c r="X44" s="47" t="n"/>
       <c r="Y44" s="35" t="n"/>
       <c r="Z44" s="37" t="n"/>
     </row>
@@ -13957,7 +13969,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X45" s="36" t="n"/>
+      <c r="X45" s="47" t="n"/>
       <c r="Y45" s="35" t="n"/>
       <c r="Z45" s="37" t="n"/>
     </row>
@@ -14068,7 +14080,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X46" s="36" t="n"/>
+      <c r="X46" s="47" t="n"/>
       <c r="Y46" s="35" t="n"/>
       <c r="Z46" s="37" t="n"/>
     </row>
@@ -14183,7 +14195,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X47" s="36" t="n"/>
+      <c r="X47" s="47" t="n"/>
       <c r="Y47" s="35" t="n"/>
       <c r="Z47" s="37" t="n"/>
     </row>
@@ -14301,7 +14313,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X48" s="36" t="n"/>
+      <c r="X48" s="47" t="n"/>
       <c r="Y48" s="35" t="n"/>
       <c r="Z48" s="37" t="n"/>
     </row>
@@ -14419,7 +14431,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X49" s="36" t="n"/>
+      <c r="X49" s="47" t="n"/>
       <c r="Y49" s="35" t="n"/>
       <c r="Z49" s="37" t="n"/>
     </row>
@@ -14521,7 +14533,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X50" s="36" t="n"/>
+      <c r="X50" s="47" t="n"/>
       <c r="Y50" s="35" t="n"/>
       <c r="Z50" s="37" t="n"/>
     </row>
@@ -14635,7 +14647,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X51" s="36" t="n"/>
+      <c r="X51" s="47" t="n"/>
       <c r="Y51" s="35" t="n"/>
       <c r="Z51" s="37" t="n"/>
     </row>
@@ -14750,7 +14762,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X52" s="36" t="n"/>
+      <c r="X52" s="47" t="n"/>
       <c r="Y52" s="35" t="n"/>
       <c r="Z52" s="37" t="n"/>
     </row>
@@ -14868,7 +14880,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X53" s="36" t="n"/>
+      <c r="X53" s="47" t="n"/>
       <c r="Y53" s="35" t="n"/>
       <c r="Z53" s="37" t="n"/>
     </row>
@@ -14982,7 +14994,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X54" s="36" t="n"/>
+      <c r="X54" s="47" t="n"/>
       <c r="Y54" s="35" t="n"/>
       <c r="Z54" s="37" t="n"/>
     </row>
@@ -15092,7 +15104,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X55" s="36" t="n"/>
+      <c r="X55" s="47" t="n"/>
       <c r="Y55" s="35" t="n"/>
       <c r="Z55" s="37" t="n"/>
     </row>
@@ -15206,7 +15218,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X56" s="36" t="n"/>
+      <c r="X56" s="47" t="n"/>
       <c r="Y56" s="35" t="n"/>
       <c r="Z56" s="37" t="n"/>
     </row>
@@ -15316,7 +15328,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X57" s="36" t="n"/>
+      <c r="X57" s="47" t="n"/>
       <c r="Y57" s="35" t="n"/>
       <c r="Z57" s="37" t="n"/>
     </row>
@@ -15430,7 +15442,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X58" s="36" t="n"/>
+      <c r="X58" s="47" t="n"/>
       <c r="Y58" s="35" t="n"/>
       <c r="Z58" s="37" t="n"/>
     </row>
@@ -15544,7 +15556,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X59" s="36" t="n"/>
+      <c r="X59" s="47" t="n"/>
       <c r="Y59" s="35" t="n"/>
       <c r="Z59" s="37" t="n"/>
     </row>
@@ -15658,7 +15670,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X60" s="36" t="n"/>
+      <c r="X60" s="47" t="n"/>
       <c r="Y60" s="35" t="n"/>
       <c r="Z60" s="37" t="n"/>
     </row>
@@ -15780,7 +15792,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X61" s="36" t="n"/>
+      <c r="X61" s="47" t="n"/>
       <c r="Y61" s="35" t="n"/>
       <c r="Z61" s="37" t="n"/>
     </row>
@@ -15895,12 +15907,18 @@
       </c>
       <c r="W62" s="35" t="inlineStr">
         <is>
-          <t>Not contacted</t>
-        </is>
-      </c>
-      <c r="X62" s="36" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="X62" s="47" t="n">
+        <v>46232</v>
+      </c>
       <c r="Y62" s="35" t="n"/>
-      <c r="Z62" s="37" t="n"/>
+      <c r="Z62" s="37" t="inlineStr">
+        <is>
+          <t>Sent 29-Jul-2026 07:54 from Outlook, cc Haffar, Tahir, Kayacan, Nesren. Delivered, no bounce.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="38" t="inlineStr">
@@ -16020,7 +16038,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X63" s="36" t="n"/>
+      <c r="X63" s="47" t="n"/>
       <c r="Y63" s="35" t="n"/>
       <c r="Z63" s="37" t="n"/>
     </row>
@@ -16130,7 +16148,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X64" s="36" t="n"/>
+      <c r="X64" s="47" t="n"/>
       <c r="Y64" s="35" t="n"/>
       <c r="Z64" s="37" t="n"/>
     </row>
@@ -16244,7 +16262,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X65" s="36" t="n"/>
+      <c r="X65" s="47" t="n"/>
       <c r="Y65" s="35" t="n"/>
       <c r="Z65" s="37" t="n"/>
     </row>
@@ -16362,7 +16380,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X66" s="36" t="n"/>
+      <c r="X66" s="47" t="n"/>
       <c r="Y66" s="35" t="n"/>
       <c r="Z66" s="37" t="n"/>
     </row>
@@ -16476,7 +16494,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X67" s="36" t="n"/>
+      <c r="X67" s="47" t="n"/>
       <c r="Y67" s="35" t="n"/>
       <c r="Z67" s="37" t="n"/>
     </row>
@@ -16590,7 +16608,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X68" s="36" t="n"/>
+      <c r="X68" s="47" t="n"/>
       <c r="Y68" s="35" t="n"/>
       <c r="Z68" s="37" t="n"/>
     </row>
@@ -16704,7 +16722,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X69" s="36" t="n"/>
+      <c r="X69" s="47" t="n"/>
       <c r="Y69" s="35" t="n"/>
       <c r="Z69" s="37" t="n"/>
     </row>
@@ -16818,7 +16836,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X70" s="36" t="n"/>
+      <c r="X70" s="47" t="n"/>
       <c r="Y70" s="35" t="n"/>
       <c r="Z70" s="37" t="n"/>
     </row>
@@ -16933,7 +16951,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X71" s="36" t="n"/>
+      <c r="X71" s="47" t="n"/>
       <c r="Y71" s="35" t="n"/>
       <c r="Z71" s="37" t="n"/>
     </row>
@@ -17047,7 +17065,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X72" s="36" t="n"/>
+      <c r="X72" s="47" t="n"/>
       <c r="Y72" s="35" t="n"/>
       <c r="Z72" s="37" t="n"/>
     </row>
@@ -17161,7 +17179,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X73" s="36" t="n"/>
+      <c r="X73" s="47" t="n"/>
       <c r="Y73" s="35" t="n"/>
       <c r="Z73" s="37" t="n"/>
     </row>
@@ -17275,7 +17293,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X74" s="36" t="n"/>
+      <c r="X74" s="47" t="n"/>
       <c r="Y74" s="35" t="n"/>
       <c r="Z74" s="37" t="n"/>
     </row>
@@ -17393,7 +17411,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X75" s="36" t="n"/>
+      <c r="X75" s="47" t="n"/>
       <c r="Y75" s="35" t="n"/>
       <c r="Z75" s="37" t="n"/>
     </row>
@@ -17503,7 +17521,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X76" s="36" t="n"/>
+      <c r="X76" s="47" t="n"/>
       <c r="Y76" s="35" t="n"/>
       <c r="Z76" s="37" t="n"/>
     </row>
@@ -17613,7 +17631,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X77" s="36" t="n"/>
+      <c r="X77" s="47" t="n"/>
       <c r="Y77" s="35" t="n"/>
       <c r="Z77" s="37" t="n"/>
     </row>
@@ -17727,7 +17745,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X78" s="36" t="n"/>
+      <c r="X78" s="47" t="n"/>
       <c r="Y78" s="35" t="n"/>
       <c r="Z78" s="37" t="n"/>
     </row>
@@ -17841,7 +17859,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X79" s="36" t="n"/>
+      <c r="X79" s="47" t="n"/>
       <c r="Y79" s="35" t="n"/>
       <c r="Z79" s="37" t="n"/>
     </row>
@@ -17955,7 +17973,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X80" s="36" t="n"/>
+      <c r="X80" s="47" t="n"/>
       <c r="Y80" s="35" t="n"/>
       <c r="Z80" s="37" t="n"/>
     </row>
@@ -18077,7 +18095,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X81" s="36" t="n"/>
+      <c r="X81" s="47" t="n"/>
       <c r="Y81" s="35" t="n"/>
       <c r="Z81" s="37" t="n"/>
     </row>
@@ -18199,7 +18217,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X82" s="36" t="n"/>
+      <c r="X82" s="47" t="n"/>
       <c r="Y82" s="35" t="n"/>
       <c r="Z82" s="37" t="n"/>
     </row>
@@ -18317,7 +18335,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X83" s="36" t="n"/>
+      <c r="X83" s="47" t="n"/>
       <c r="Y83" s="35" t="n"/>
       <c r="Z83" s="37" t="n"/>
     </row>
@@ -18439,7 +18457,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X84" s="36" t="n"/>
+      <c r="X84" s="47" t="n"/>
       <c r="Y84" s="35" t="n"/>
       <c r="Z84" s="37" t="n"/>
     </row>
@@ -18557,7 +18575,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X85" s="36" t="n"/>
+      <c r="X85" s="47" t="n"/>
       <c r="Y85" s="35" t="n"/>
       <c r="Z85" s="37" t="n"/>
     </row>
@@ -18675,7 +18693,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X86" s="36" t="n"/>
+      <c r="X86" s="47" t="n"/>
       <c r="Y86" s="35" t="n"/>
       <c r="Z86" s="37" t="n"/>
     </row>
@@ -18789,7 +18807,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X87" s="36" t="n"/>
+      <c r="X87" s="47" t="n"/>
       <c r="Y87" s="35" t="n"/>
       <c r="Z87" s="37" t="n"/>
     </row>
@@ -18911,7 +18929,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X88" s="36" t="n"/>
+      <c r="X88" s="47" t="n"/>
       <c r="Y88" s="35" t="n"/>
       <c r="Z88" s="37" t="n"/>
     </row>
@@ -19029,7 +19047,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X89" s="36" t="n"/>
+      <c r="X89" s="47" t="n"/>
       <c r="Y89" s="35" t="n"/>
       <c r="Z89" s="37" t="n"/>
     </row>
@@ -19147,7 +19165,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X90" s="36" t="n"/>
+      <c r="X90" s="47" t="n"/>
       <c r="Y90" s="35" t="n"/>
       <c r="Z90" s="37" t="n"/>
     </row>
@@ -19269,7 +19287,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X91" s="36" t="n"/>
+      <c r="X91" s="47" t="n"/>
       <c r="Y91" s="35" t="n"/>
       <c r="Z91" s="37" t="n"/>
     </row>
@@ -19387,7 +19405,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X92" s="36" t="n"/>
+      <c r="X92" s="47" t="n"/>
       <c r="Y92" s="35" t="n"/>
       <c r="Z92" s="37" t="n"/>
     </row>
@@ -19501,7 +19519,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X93" s="36" t="n"/>
+      <c r="X93" s="47" t="n"/>
       <c r="Y93" s="35" t="n"/>
       <c r="Z93" s="37" t="n"/>
     </row>
@@ -19619,7 +19637,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X94" s="36" t="n"/>
+      <c r="X94" s="47" t="n"/>
       <c r="Y94" s="35" t="n"/>
       <c r="Z94" s="37" t="n"/>
     </row>
@@ -19733,7 +19751,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X95" s="36" t="n"/>
+      <c r="X95" s="47" t="n"/>
       <c r="Y95" s="35" t="n"/>
       <c r="Z95" s="37" t="n"/>
     </row>
@@ -19847,7 +19865,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X96" s="36" t="n"/>
+      <c r="X96" s="47" t="n"/>
       <c r="Y96" s="35" t="n"/>
       <c r="Z96" s="37" t="n"/>
     </row>
@@ -19961,7 +19979,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X97" s="36" t="n"/>
+      <c r="X97" s="47" t="n"/>
       <c r="Y97" s="35" t="n"/>
       <c r="Z97" s="37" t="n"/>
     </row>
@@ -20075,7 +20093,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X98" s="36" t="n"/>
+      <c r="X98" s="47" t="n"/>
       <c r="Y98" s="35" t="n"/>
       <c r="Z98" s="37" t="n"/>
     </row>
@@ -20185,7 +20203,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X99" s="36" t="n"/>
+      <c r="X99" s="47" t="n"/>
       <c r="Y99" s="35" t="n"/>
       <c r="Z99" s="37" t="n"/>
     </row>
@@ -20295,7 +20313,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X100" s="36" t="n"/>
+      <c r="X100" s="47" t="n"/>
       <c r="Y100" s="35" t="n"/>
       <c r="Z100" s="37" t="n"/>
     </row>
@@ -20409,7 +20427,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X101" s="36" t="n"/>
+      <c r="X101" s="47" t="n"/>
       <c r="Y101" s="35" t="n"/>
       <c r="Z101" s="37" t="n"/>
     </row>
@@ -20527,7 +20545,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X102" s="36" t="n"/>
+      <c r="X102" s="47" t="n"/>
       <c r="Y102" s="35" t="n"/>
       <c r="Z102" s="37" t="n"/>
     </row>
@@ -20641,7 +20659,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X103" s="36" t="n"/>
+      <c r="X103" s="47" t="n"/>
       <c r="Y103" s="35" t="n"/>
       <c r="Z103" s="37" t="n"/>
     </row>
@@ -20755,7 +20773,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X104" s="36" t="n"/>
+      <c r="X104" s="47" t="n"/>
       <c r="Y104" s="35" t="n"/>
       <c r="Z104" s="37" t="n"/>
     </row>
@@ -20873,7 +20891,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X105" s="36" t="n"/>
+      <c r="X105" s="47" t="n"/>
       <c r="Y105" s="35" t="n"/>
       <c r="Z105" s="37" t="n"/>
     </row>
@@ -20987,7 +21005,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X106" s="36" t="n"/>
+      <c r="X106" s="47" t="n"/>
       <c r="Y106" s="35" t="n"/>
       <c r="Z106" s="37" t="n"/>
     </row>
@@ -21097,7 +21115,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X107" s="36" t="n"/>
+      <c r="X107" s="47" t="n"/>
       <c r="Y107" s="35" t="n"/>
       <c r="Z107" s="37" t="n"/>
     </row>
@@ -21211,7 +21229,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X108" s="36" t="n"/>
+      <c r="X108" s="47" t="n"/>
       <c r="Y108" s="35" t="n"/>
       <c r="Z108" s="37" t="n"/>
     </row>
@@ -21317,7 +21335,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X109" s="36" t="n"/>
+      <c r="X109" s="47" t="n"/>
       <c r="Y109" s="35" t="n"/>
       <c r="Z109" s="37" t="n"/>
     </row>
@@ -21423,7 +21441,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X110" s="36" t="n"/>
+      <c r="X110" s="47" t="n"/>
       <c r="Y110" s="35" t="n"/>
       <c r="Z110" s="37" t="n"/>
     </row>
@@ -21533,7 +21551,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X111" s="36" t="n"/>
+      <c r="X111" s="47" t="n"/>
       <c r="Y111" s="35" t="n"/>
       <c r="Z111" s="37" t="n"/>
     </row>
@@ -21647,7 +21665,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X112" s="36" t="n"/>
+      <c r="X112" s="47" t="n"/>
       <c r="Y112" s="35" t="n"/>
       <c r="Z112" s="37" t="n"/>
     </row>
@@ -21761,7 +21779,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X113" s="36" t="n"/>
+      <c r="X113" s="47" t="n"/>
       <c r="Y113" s="35" t="n"/>
       <c r="Z113" s="37" t="n"/>
     </row>
@@ -21875,7 +21893,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X114" s="36" t="n"/>
+      <c r="X114" s="47" t="n"/>
       <c r="Y114" s="35" t="n"/>
       <c r="Z114" s="37" t="n"/>
     </row>
@@ -21989,7 +22007,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X115" s="36" t="n"/>
+      <c r="X115" s="47" t="n"/>
       <c r="Y115" s="35" t="n"/>
       <c r="Z115" s="37" t="n"/>
     </row>
@@ -22099,7 +22117,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X116" s="36" t="n"/>
+      <c r="X116" s="47" t="n"/>
       <c r="Y116" s="35" t="n"/>
       <c r="Z116" s="37" t="n"/>
     </row>
@@ -22214,7 +22232,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X117" s="36" t="n"/>
+      <c r="X117" s="47" t="n"/>
       <c r="Y117" s="35" t="n"/>
       <c r="Z117" s="37" t="n"/>
     </row>
@@ -22328,7 +22346,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X118" s="36" t="n"/>
+      <c r="X118" s="47" t="n"/>
       <c r="Y118" s="35" t="n"/>
       <c r="Z118" s="37" t="n"/>
     </row>
@@ -22446,7 +22464,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X119" s="36" t="n"/>
+      <c r="X119" s="47" t="n"/>
       <c r="Y119" s="35" t="n"/>
       <c r="Z119" s="37" t="n"/>
     </row>
@@ -22564,7 +22582,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X120" s="36" t="n"/>
+      <c r="X120" s="47" t="n"/>
       <c r="Y120" s="35" t="n"/>
       <c r="Z120" s="37" t="n"/>
     </row>
@@ -22679,7 +22697,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X121" s="36" t="n"/>
+      <c r="X121" s="47" t="n"/>
       <c r="Y121" s="35" t="n"/>
       <c r="Z121" s="37" t="n"/>
     </row>
@@ -22797,7 +22815,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X122" s="36" t="n"/>
+      <c r="X122" s="47" t="n"/>
       <c r="Y122" s="35" t="n"/>
       <c r="Z122" s="37" t="n"/>
     </row>
@@ -22911,7 +22929,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X123" s="36" t="n"/>
+      <c r="X123" s="47" t="n"/>
       <c r="Y123" s="35" t="n"/>
       <c r="Z123" s="37" t="n"/>
     </row>
@@ -23021,7 +23039,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X124" s="36" t="n"/>
+      <c r="X124" s="47" t="n"/>
       <c r="Y124" s="35" t="n"/>
       <c r="Z124" s="37" t="n"/>
     </row>
@@ -23136,7 +23154,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X125" s="36" t="n"/>
+      <c r="X125" s="47" t="n"/>
       <c r="Y125" s="35" t="n"/>
       <c r="Z125" s="37" t="n"/>
     </row>
@@ -23254,7 +23272,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X126" s="36" t="n"/>
+      <c r="X126" s="47" t="n"/>
       <c r="Y126" s="35" t="n"/>
       <c r="Z126" s="37" t="n"/>
     </row>
@@ -23373,7 +23391,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X127" s="36" t="n"/>
+      <c r="X127" s="47" t="n"/>
       <c r="Y127" s="35" t="n"/>
       <c r="Z127" s="37" t="n"/>
     </row>
@@ -23483,7 +23501,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X128" s="36" t="n"/>
+      <c r="X128" s="47" t="n"/>
       <c r="Y128" s="35" t="n"/>
       <c r="Z128" s="37" t="n"/>
     </row>
@@ -23598,7 +23616,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X129" s="36" t="n"/>
+      <c r="X129" s="47" t="n"/>
       <c r="Y129" s="35" t="n"/>
       <c r="Z129" s="37" t="n"/>
     </row>
@@ -23713,7 +23731,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X130" s="36" t="n"/>
+      <c r="X130" s="47" t="n"/>
       <c r="Y130" s="35" t="n"/>
       <c r="Z130" s="37" t="n"/>
     </row>
@@ -23827,7 +23845,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X131" s="36" t="n"/>
+      <c r="X131" s="47" t="n"/>
       <c r="Y131" s="35" t="n"/>
       <c r="Z131" s="37" t="n"/>
     </row>
@@ -23941,7 +23959,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X132" s="36" t="n"/>
+      <c r="X132" s="47" t="n"/>
       <c r="Y132" s="35" t="n"/>
       <c r="Z132" s="37" t="n"/>
     </row>
@@ -24059,7 +24077,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X133" s="36" t="n"/>
+      <c r="X133" s="47" t="n"/>
       <c r="Y133" s="35" t="n"/>
       <c r="Z133" s="37" t="n"/>
     </row>
@@ -24177,7 +24195,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X134" s="36" t="n"/>
+      <c r="X134" s="47" t="n"/>
       <c r="Y134" s="35" t="n"/>
       <c r="Z134" s="37" t="n"/>
     </row>
@@ -24295,7 +24313,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X135" s="36" t="n"/>
+      <c r="X135" s="47" t="n"/>
       <c r="Y135" s="35" t="n"/>
       <c r="Z135" s="37" t="n"/>
     </row>
@@ -24413,7 +24431,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X136" s="36" t="n"/>
+      <c r="X136" s="47" t="n"/>
       <c r="Y136" s="35" t="n"/>
       <c r="Z136" s="37" t="n"/>
     </row>
@@ -24531,7 +24549,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X137" s="36" t="n"/>
+      <c r="X137" s="47" t="n"/>
       <c r="Y137" s="35" t="n"/>
       <c r="Z137" s="37" t="n"/>
     </row>
@@ -24646,7 +24664,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X138" s="36" t="n"/>
+      <c r="X138" s="47" t="n"/>
       <c r="Y138" s="35" t="n"/>
       <c r="Z138" s="37" t="n"/>
     </row>
@@ -24756,7 +24774,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X139" s="36" t="n"/>
+      <c r="X139" s="47" t="n"/>
       <c r="Y139" s="35" t="n"/>
       <c r="Z139" s="37" t="n"/>
     </row>
@@ -24870,7 +24888,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X140" s="36" t="n"/>
+      <c r="X140" s="47" t="n"/>
       <c r="Y140" s="35" t="n"/>
       <c r="Z140" s="37" t="n"/>
     </row>
@@ -24984,7 +25002,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X141" s="36" t="n"/>
+      <c r="X141" s="47" t="n"/>
       <c r="Y141" s="35" t="n"/>
       <c r="Z141" s="37" t="n"/>
     </row>
@@ -25094,7 +25112,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X142" s="36" t="n"/>
+      <c r="X142" s="47" t="n"/>
       <c r="Y142" s="35" t="n"/>
       <c r="Z142" s="37" t="n"/>
     </row>
@@ -25201,7 +25219,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X143" s="36" t="n"/>
+      <c r="X143" s="47" t="n"/>
       <c r="Y143" s="35" t="n"/>
       <c r="Z143" s="37" t="n"/>
     </row>
@@ -25319,7 +25337,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X144" s="36" t="n"/>
+      <c r="X144" s="47" t="n"/>
       <c r="Y144" s="35" t="n"/>
       <c r="Z144" s="37" t="n"/>
     </row>
@@ -25433,7 +25451,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X145" s="36" t="n"/>
+      <c r="X145" s="47" t="n"/>
       <c r="Y145" s="35" t="n"/>
       <c r="Z145" s="37" t="n"/>
     </row>
@@ -25547,7 +25565,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X146" s="36" t="n"/>
+      <c r="X146" s="47" t="n"/>
       <c r="Y146" s="35" t="n"/>
       <c r="Z146" s="37" t="n"/>
     </row>
@@ -25661,7 +25679,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X147" s="36" t="n"/>
+      <c r="X147" s="47" t="n"/>
       <c r="Y147" s="35" t="n"/>
       <c r="Z147" s="37" t="n"/>
     </row>
@@ -25780,7 +25798,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X148" s="36" t="n"/>
+      <c r="X148" s="47" t="n"/>
       <c r="Y148" s="35" t="n"/>
       <c r="Z148" s="37" t="n"/>
     </row>
@@ -25894,7 +25912,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X149" s="36" t="n"/>
+      <c r="X149" s="47" t="n"/>
       <c r="Y149" s="35" t="n"/>
       <c r="Z149" s="37" t="n"/>
     </row>
@@ -26009,7 +26027,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X150" s="36" t="n"/>
+      <c r="X150" s="47" t="n"/>
       <c r="Y150" s="35" t="n"/>
       <c r="Z150" s="37" t="n"/>
     </row>
@@ -26127,7 +26145,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X151" s="36" t="n"/>
+      <c r="X151" s="47" t="n"/>
       <c r="Y151" s="35" t="n"/>
       <c r="Z151" s="37" t="n"/>
     </row>
@@ -26245,7 +26263,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X152" s="36" t="n"/>
+      <c r="X152" s="47" t="n"/>
       <c r="Y152" s="35" t="n"/>
       <c r="Z152" s="37" t="n"/>
     </row>
@@ -26355,7 +26373,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X153" s="36" t="n"/>
+      <c r="X153" s="47" t="n"/>
       <c r="Y153" s="35" t="n"/>
       <c r="Z153" s="37" t="n"/>
     </row>
@@ -26469,7 +26487,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X154" s="36" t="n"/>
+      <c r="X154" s="47" t="n"/>
       <c r="Y154" s="35" t="n"/>
       <c r="Z154" s="37" t="n"/>
     </row>
@@ -26579,7 +26597,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X155" s="36" t="n"/>
+      <c r="X155" s="47" t="n"/>
       <c r="Y155" s="35" t="n"/>
       <c r="Z155" s="37" t="n"/>
     </row>
@@ -26693,7 +26711,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X156" s="36" t="n"/>
+      <c r="X156" s="47" t="n"/>
       <c r="Y156" s="35" t="n"/>
       <c r="Z156" s="37" t="n"/>
     </row>
@@ -26812,7 +26830,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X157" s="36" t="n"/>
+      <c r="X157" s="47" t="n"/>
       <c r="Y157" s="35" t="n"/>
       <c r="Z157" s="37" t="n"/>
     </row>
@@ -26931,7 +26949,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X158" s="36" t="n"/>
+      <c r="X158" s="47" t="n"/>
       <c r="Y158" s="35" t="n"/>
       <c r="Z158" s="37" t="n"/>
     </row>
@@ -27049,7 +27067,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X159" s="36" t="n"/>
+      <c r="X159" s="47" t="n"/>
       <c r="Y159" s="35" t="n"/>
       <c r="Z159" s="37" t="n"/>
     </row>
@@ -27168,7 +27186,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X160" s="36" t="n"/>
+      <c r="X160" s="47" t="n"/>
       <c r="Y160" s="35" t="n"/>
       <c r="Z160" s="37" t="n"/>
     </row>
@@ -27290,7 +27308,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X161" s="36" t="n"/>
+      <c r="X161" s="47" t="n"/>
       <c r="Y161" s="35" t="n"/>
       <c r="Z161" s="37" t="n"/>
     </row>
@@ -27404,7 +27422,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X162" s="36" t="n"/>
+      <c r="X162" s="47" t="n"/>
       <c r="Y162" s="35" t="n"/>
       <c r="Z162" s="37" t="n"/>
     </row>
@@ -27518,7 +27536,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X163" s="36" t="n"/>
+      <c r="X163" s="47" t="n"/>
       <c r="Y163" s="35" t="n"/>
       <c r="Z163" s="37" t="n"/>
     </row>
@@ -27640,7 +27658,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X164" s="36" t="n"/>
+      <c r="X164" s="47" t="n"/>
       <c r="Y164" s="35" t="n"/>
       <c r="Z164" s="37" t="n"/>
     </row>
@@ -27754,7 +27772,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X165" s="36" t="n"/>
+      <c r="X165" s="47" t="n"/>
       <c r="Y165" s="35" t="n"/>
       <c r="Z165" s="37" t="n"/>
     </row>
@@ -27868,7 +27886,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X166" s="36" t="n"/>
+      <c r="X166" s="47" t="n"/>
       <c r="Y166" s="35" t="n"/>
       <c r="Z166" s="37" t="n"/>
     </row>
@@ -27978,7 +27996,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X167" s="36" t="n"/>
+      <c r="X167" s="47" t="n"/>
       <c r="Y167" s="35" t="n"/>
       <c r="Z167" s="37" t="n"/>
     </row>
@@ -28092,7 +28110,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X168" s="36" t="n"/>
+      <c r="X168" s="47" t="n"/>
       <c r="Y168" s="35" t="n"/>
       <c r="Z168" s="37" t="n"/>
     </row>
@@ -28211,7 +28229,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X169" s="36" t="n"/>
+      <c r="X169" s="47" t="n"/>
       <c r="Y169" s="35" t="n"/>
       <c r="Z169" s="37" t="n"/>
     </row>
@@ -28318,12 +28336,18 @@
       <c r="V170" s="24" t="inlineStr"/>
       <c r="W170" s="35" t="inlineStr">
         <is>
-          <t>Not contacted</t>
-        </is>
-      </c>
-      <c r="X170" s="36" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="X170" s="47" t="n">
+        <v>46232</v>
+      </c>
       <c r="Y170" s="35" t="n"/>
-      <c r="Z170" s="37" t="n"/>
+      <c r="Z170" s="37" t="inlineStr">
+        <is>
+          <t>Sent 29-Jul-2026 07:42 from Outlook, cc Haffar, Nesren. Delivered, no bounce.</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="38" t="inlineStr">
@@ -28435,7 +28459,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X171" s="36" t="n"/>
+      <c r="X171" s="47" t="n"/>
       <c r="Y171" s="35" t="n"/>
       <c r="Z171" s="37" t="n"/>
     </row>
@@ -28549,7 +28573,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X172" s="36" t="n"/>
+      <c r="X172" s="47" t="n"/>
       <c r="Y172" s="35" t="n"/>
       <c r="Z172" s="37" t="n"/>
     </row>
@@ -28667,7 +28691,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X173" s="36" t="n"/>
+      <c r="X173" s="47" t="n"/>
       <c r="Y173" s="35" t="n"/>
       <c r="Z173" s="37" t="n"/>
     </row>
@@ -28777,7 +28801,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X174" s="36" t="n"/>
+      <c r="X174" s="47" t="n"/>
       <c r="Y174" s="35" t="n"/>
       <c r="Z174" s="37" t="n"/>
     </row>
@@ -28891,7 +28915,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X175" s="36" t="n"/>
+      <c r="X175" s="47" t="n"/>
       <c r="Y175" s="35" t="n"/>
       <c r="Z175" s="37" t="n"/>
     </row>
@@ -29010,7 +29034,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X176" s="36" t="n"/>
+      <c r="X176" s="47" t="n"/>
       <c r="Y176" s="35" t="n"/>
       <c r="Z176" s="37" t="n"/>
     </row>
@@ -29120,7 +29144,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X177" s="36" t="n"/>
+      <c r="X177" s="47" t="n"/>
       <c r="Y177" s="35" t="n"/>
       <c r="Z177" s="37" t="n"/>
     </row>
@@ -29234,7 +29258,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X178" s="36" t="n"/>
+      <c r="X178" s="47" t="n"/>
       <c r="Y178" s="35" t="n"/>
       <c r="Z178" s="37" t="n"/>
     </row>
@@ -29345,7 +29369,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X179" s="36" t="n"/>
+      <c r="X179" s="47" t="n"/>
       <c r="Y179" s="35" t="n"/>
       <c r="Z179" s="37" t="n"/>
     </row>
@@ -29456,7 +29480,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X180" s="36" t="n"/>
+      <c r="X180" s="47" t="n"/>
       <c r="Y180" s="35" t="n"/>
       <c r="Z180" s="37" t="n"/>
     </row>
@@ -29562,7 +29586,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X181" s="36" t="n"/>
+      <c r="X181" s="47" t="n"/>
       <c r="Y181" s="35" t="n"/>
       <c r="Z181" s="37" t="n"/>
     </row>
@@ -29680,7 +29704,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X182" s="36" t="n"/>
+      <c r="X182" s="47" t="n"/>
       <c r="Y182" s="35" t="n"/>
       <c r="Z182" s="37" t="n"/>
     </row>
@@ -29794,7 +29818,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X183" s="36" t="n"/>
+      <c r="X183" s="47" t="n"/>
       <c r="Y183" s="35" t="n"/>
       <c r="Z183" s="37" t="n"/>
     </row>
@@ -29912,7 +29936,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X184" s="36" t="n"/>
+      <c r="X184" s="47" t="n"/>
       <c r="Y184" s="35" t="n"/>
       <c r="Z184" s="37" t="n"/>
     </row>
@@ -30022,7 +30046,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X185" s="36" t="n"/>
+      <c r="X185" s="47" t="n"/>
       <c r="Y185" s="35" t="n"/>
       <c r="Z185" s="37" t="n"/>
     </row>
@@ -30136,7 +30160,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X186" s="36" t="n"/>
+      <c r="X186" s="47" t="n"/>
       <c r="Y186" s="35" t="n"/>
       <c r="Z186" s="37" t="n"/>
     </row>
@@ -30255,7 +30279,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X187" s="36" t="n"/>
+      <c r="X187" s="47" t="n"/>
       <c r="Y187" s="35" t="n"/>
       <c r="Z187" s="37" t="n"/>
     </row>
@@ -30361,7 +30385,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X188" s="36" t="n"/>
+      <c r="X188" s="47" t="n"/>
       <c r="Y188" s="35" t="n"/>
       <c r="Z188" s="37" t="n"/>
     </row>
@@ -30467,7 +30491,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X189" s="36" t="n"/>
+      <c r="X189" s="47" t="n"/>
       <c r="Y189" s="35" t="n"/>
       <c r="Z189" s="37" t="n"/>
     </row>
@@ -30585,7 +30609,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X190" s="36" t="n"/>
+      <c r="X190" s="47" t="n"/>
       <c r="Y190" s="35" t="n"/>
       <c r="Z190" s="37" t="n"/>
     </row>
@@ -30699,7 +30723,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X191" s="36" t="n"/>
+      <c r="X191" s="47" t="n"/>
       <c r="Y191" s="35" t="n"/>
       <c r="Z191" s="37" t="n"/>
     </row>
@@ -30813,7 +30837,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X192" s="36" t="n"/>
+      <c r="X192" s="47" t="n"/>
       <c r="Y192" s="35" t="n"/>
       <c r="Z192" s="37" t="n"/>
     </row>
@@ -30923,7 +30947,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X193" s="36" t="n"/>
+      <c r="X193" s="47" t="n"/>
       <c r="Y193" s="35" t="n"/>
       <c r="Z193" s="37" t="n"/>
     </row>
@@ -31037,7 +31061,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X194" s="36" t="n"/>
+      <c r="X194" s="47" t="n"/>
       <c r="Y194" s="35" t="n"/>
       <c r="Z194" s="37" t="n"/>
     </row>
@@ -31147,7 +31171,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X195" s="36" t="n"/>
+      <c r="X195" s="47" t="n"/>
       <c r="Y195" s="35" t="n"/>
       <c r="Z195" s="37" t="n"/>
     </row>
@@ -31265,7 +31289,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X196" s="36" t="n"/>
+      <c r="X196" s="47" t="n"/>
       <c r="Y196" s="35" t="n"/>
       <c r="Z196" s="37" t="n"/>
     </row>
@@ -31383,7 +31407,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X197" s="36" t="n"/>
+      <c r="X197" s="47" t="n"/>
       <c r="Y197" s="35" t="n"/>
       <c r="Z197" s="37" t="n"/>
     </row>
@@ -31493,7 +31517,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X198" s="36" t="n"/>
+      <c r="X198" s="47" t="n"/>
       <c r="Y198" s="35" t="n"/>
       <c r="Z198" s="37" t="n"/>
     </row>
@@ -31607,7 +31631,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X199" s="36" t="n"/>
+      <c r="X199" s="47" t="n"/>
       <c r="Y199" s="35" t="n"/>
       <c r="Z199" s="37" t="n"/>
     </row>
@@ -31721,7 +31745,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X200" s="36" t="n"/>
+      <c r="X200" s="47" t="n"/>
       <c r="Y200" s="35" t="n"/>
       <c r="Z200" s="37" t="n"/>
     </row>
@@ -31831,7 +31855,7 @@
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="X201" s="36" t="n"/>
+      <c r="X201" s="47" t="n"/>
       <c r="Y201" s="35" t="n"/>
       <c r="Z201" s="37" t="n"/>
     </row>
